--- a/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EECB552-B1BC-F84C-8406-FA498FAAF4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB13344-461F-0349-86DF-F6BB1EC7E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="37600" windowHeight="19620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,29 +18,29 @@
     <sheet name="MI_Energy" sheetId="2" r:id="rId3"/>
     <sheet name="MS_Energy_Disag" sheetId="3" r:id="rId4"/>
     <sheet name="MI_Vehicles" sheetId="4" r:id="rId5"/>
-    <sheet name="MI_Vehicles_Bieuville" sheetId="5" r:id="rId6"/>
-    <sheet name="MI_Vehicles_Bieuville_Clean" sheetId="6" r:id="rId7"/>
-    <sheet name="MS_Battery_Motor_LDV" sheetId="7" r:id="rId8"/>
-    <sheet name="MI_Vehicles_Public" sheetId="8" r:id="rId9"/>
-    <sheet name="MI_H2" sheetId="9" r:id="rId10"/>
-    <sheet name="Mapping" sheetId="11" r:id="rId11"/>
-    <sheet name="Overrides" sheetId="12" r:id="rId12"/>
-    <sheet name="Legend" sheetId="13" r:id="rId13"/>
-    <sheet name="MI" sheetId="14" r:id="rId14"/>
-    <sheet name="Battery_Capacity" sheetId="15" r:id="rId15"/>
-    <sheet name="Ref&amp;Hp" sheetId="16" r:id="rId16"/>
-    <sheet name="Power_Source_calcul" sheetId="17" r:id="rId17"/>
-    <sheet name="EV_Calcul" sheetId="18" r:id="rId18"/>
+    <sheet name="MI_Vehicles_Bieuville_Clean" sheetId="6" r:id="rId6"/>
+    <sheet name="MS_Battery_Motor_LDV" sheetId="7" r:id="rId7"/>
+    <sheet name="MI_Vehicles_Public" sheetId="8" r:id="rId8"/>
+    <sheet name="MI_H2" sheetId="9" r:id="rId9"/>
+    <sheet name="Mapping" sheetId="11" r:id="rId10"/>
+    <sheet name="Overrides" sheetId="12" r:id="rId11"/>
+    <sheet name="Legend" sheetId="13" r:id="rId12"/>
+    <sheet name="MI" sheetId="14" r:id="rId13"/>
+    <sheet name="Battery_Capacity" sheetId="15" r:id="rId14"/>
+    <sheet name="Ref&amp;Hp" sheetId="16" r:id="rId15"/>
+    <sheet name="Power_Source_calcul" sheetId="17" r:id="rId16"/>
+    <sheet name="EV_Calcul" sheetId="18" r:id="rId17"/>
+    <sheet name="MI_Vehicles_Bieuville" sheetId="5" r:id="rId18"/>
     <sheet name="MS_Energy_Ag" sheetId="19" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Battery_Capacity!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Mapping!$A$1:$H$691</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">MI!$A$1:$G$829</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Battery_Capacity!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Mapping!$A$1:$H$691</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">MI!$A$1:$G$829</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MI_Energy!$A$1:$AG$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">MS_Energy_Ag!$A$1:$S$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MS_Energy_Disag!$A$1:$AF$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Overrides!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Overrides!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5881,6 +5881,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF305496"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6586,635 +6591,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF46BECF"/>
-  </sheetPr>
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.33203125" customWidth="1"/>
-    <col min="13" max="13" width="23.33203125" customWidth="1"/>
-    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="92" t="s">
-        <v>229</v>
-      </c>
-      <c r="C1" s="92" t="s">
-        <v>230</v>
-      </c>
-      <c r="D1" s="92" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="9">
-        <v>75</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="9">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="9">
-        <v>0</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="9">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9">
-        <v>303.58</v>
-      </c>
-      <c r="D5" s="9">
-        <v>418.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="92" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="9">
-        <v>0</v>
-      </c>
-      <c r="C6" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="9">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="9">
-        <v>333</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <v>104.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="9">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="9">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="9">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="92" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="9">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="92" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="9">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="9">
-        <v>33333</v>
-      </c>
-      <c r="C15" s="9">
-        <v>1097.24</v>
-      </c>
-      <c r="D15" s="9">
-        <v>6006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="9">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="92" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="9">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="92" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="9">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="9">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9">
-        <v>78.400000000000006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="9">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="9">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="92" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="9">
-        <v>5117</v>
-      </c>
-      <c r="C22" s="9">
-        <v>191.61</v>
-      </c>
-      <c r="D22" s="9">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="9">
-        <v>0</v>
-      </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="9">
-        <v>0</v>
-      </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="92" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="9">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="92" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="9">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9">
-        <v>0</v>
-      </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="92" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="9">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="9">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9">
-        <v>0</v>
-      </c>
-      <c r="D28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="9">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="92" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="9">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9">
-        <v>0</v>
-      </c>
-      <c r="D30" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="92" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="9">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="92" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="9">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="92" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="9">
-        <v>0</v>
-      </c>
-      <c r="C33" s="9">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="92" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="9">
-        <v>0</v>
-      </c>
-      <c r="C35" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="D35" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="9">
-        <v>0</v>
-      </c>
-      <c r="C36" s="9">
-        <v>0</v>
-      </c>
-      <c r="D36" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="92" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="9">
-        <v>135</v>
-      </c>
-      <c r="C37" s="9">
-        <v>21.76</v>
-      </c>
-      <c r="D37" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="92" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="9">
-        <v>0</v>
-      </c>
-      <c r="C38" s="9">
-        <v>0</v>
-      </c>
-      <c r="D38" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="9">
-        <v>0</v>
-      </c>
-      <c r="C39" s="9">
-        <v>0</v>
-      </c>
-      <c r="D39" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="B40" s="9">
-        <v>0</v>
-      </c>
-      <c r="C40" s="9">
-        <v>0</v>
-      </c>
-      <c r="D40" s="9">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="92" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="9">
-        <v>0</v>
-      </c>
-      <c r="C41" s="9">
-        <v>0</v>
-      </c>
-      <c r="D41" s="9">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="238" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" s="9">
-        <v>0</v>
-      </c>
-      <c r="C42" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="D42" s="9">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <sheetPr filterMode="1">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:H691"/>
@@ -8086,7 +7464,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="196" t="s">
         <v>352</v>
       </c>
@@ -8100,7 +7478,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="196" t="s">
         <v>354</v>
       </c>
@@ -8114,7 +7492,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="196" t="s">
         <v>355</v>
       </c>
@@ -8128,7 +7506,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="196" t="s">
         <v>356</v>
       </c>
@@ -8142,7 +7520,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="196" t="s">
         <v>357</v>
       </c>
@@ -8156,7 +7534,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="196" t="s">
         <v>358</v>
       </c>
@@ -8170,7 +7548,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="196" t="s">
         <v>359</v>
       </c>
@@ -8184,7 +7562,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="196" t="s">
         <v>360</v>
       </c>
@@ -8198,7 +7576,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="196" t="s">
         <v>361</v>
       </c>
@@ -8212,7 +7590,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="196" t="s">
         <v>362</v>
       </c>
@@ -8226,7 +7604,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="196" t="s">
         <v>363</v>
       </c>
@@ -8240,7 +7618,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="196" t="s">
         <v>364</v>
       </c>
@@ -8254,7 +7632,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="196" t="s">
         <v>365</v>
       </c>
@@ -8268,7 +7646,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="196" t="s">
         <v>366</v>
       </c>
@@ -8282,7 +7660,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="196" t="s">
         <v>367</v>
       </c>
@@ -8296,7 +7674,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="196" t="s">
         <v>368</v>
       </c>
@@ -8310,7 +7688,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="196" t="s">
         <v>369</v>
       </c>
@@ -8324,7 +7702,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="196" t="s">
         <v>370</v>
       </c>
@@ -8338,7 +7716,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="196" t="s">
         <v>371</v>
       </c>
@@ -8352,7 +7730,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="196" t="s">
         <v>372</v>
       </c>
@@ -8366,7 +7744,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="196" t="s">
         <v>373</v>
       </c>
@@ -8380,7 +7758,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="196" t="s">
         <v>374</v>
       </c>
@@ -8394,7 +7772,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="196" t="s">
         <v>375</v>
       </c>
@@ -8408,7 +7786,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="196" t="s">
         <v>376</v>
       </c>
@@ -8422,7 +7800,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="196" t="s">
         <v>377</v>
       </c>
@@ -8436,7 +7814,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="196" t="s">
         <v>378</v>
       </c>
@@ -8450,7 +7828,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="196" t="s">
         <v>379</v>
       </c>
@@ -8464,7 +7842,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="196" t="s">
         <v>380</v>
       </c>
@@ -8478,7 +7856,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="196" t="s">
         <v>381</v>
       </c>
@@ -8492,7 +7870,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="196" t="s">
         <v>382</v>
       </c>
@@ -8506,7 +7884,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="196" t="s">
         <v>383</v>
       </c>
@@ -8520,7 +7898,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="196" t="s">
         <v>384</v>
       </c>
@@ -8534,7 +7912,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="196" t="s">
         <v>385</v>
       </c>
@@ -8548,7 +7926,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="196" t="s">
         <v>386</v>
       </c>
@@ -8562,7 +7940,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="196" t="s">
         <v>387</v>
       </c>
@@ -8576,7 +7954,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="196" t="s">
         <v>388</v>
       </c>
@@ -8590,7 +7968,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="196" t="s">
         <v>389</v>
       </c>
@@ -8604,7 +7982,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="196" t="s">
         <v>390</v>
       </c>
@@ -8618,7 +7996,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="196" t="s">
         <v>391</v>
       </c>
@@ -8632,7 +8010,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="196" t="s">
         <v>392</v>
       </c>
@@ -8646,7 +8024,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="196" t="s">
         <v>393</v>
       </c>
@@ -8660,7 +8038,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="196" t="s">
         <v>394</v>
       </c>
@@ -8674,7 +8052,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="196" t="s">
         <v>395</v>
       </c>
@@ -8688,7 +8066,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="196" t="s">
         <v>396</v>
       </c>
@@ -8702,7 +8080,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="196" t="s">
         <v>397</v>
       </c>
@@ -8716,7 +8094,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="196" t="s">
         <v>398</v>
       </c>
@@ -8730,7 +8108,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="196" t="s">
         <v>399</v>
       </c>
@@ -8744,7 +8122,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="196" t="s">
         <v>400</v>
       </c>
@@ -8758,7 +8136,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="196" t="s">
         <v>401</v>
       </c>
@@ -8772,7 +8150,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="196" t="s">
         <v>402</v>
       </c>
@@ -8786,7 +8164,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="196" t="s">
         <v>403</v>
       </c>
@@ -8800,7 +8178,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="196" t="s">
         <v>404</v>
       </c>
@@ -8814,7 +8192,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="196" t="s">
         <v>405</v>
       </c>
@@ -8828,7 +8206,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="196" t="s">
         <v>406</v>
       </c>
@@ -8842,7 +8220,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="196" t="s">
         <v>407</v>
       </c>
@@ -8856,7 +8234,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="196" t="s">
         <v>408</v>
       </c>
@@ -8870,7 +8248,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="196" t="s">
         <v>409</v>
       </c>
@@ -8884,7 +8262,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="196" t="s">
         <v>410</v>
       </c>
@@ -8898,7 +8276,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="196" t="s">
         <v>411</v>
       </c>
@@ -8912,7 +8290,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="196" t="s">
         <v>412</v>
       </c>
@@ -8926,7 +8304,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="196" t="s">
         <v>413</v>
       </c>
@@ -8940,7 +8318,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="196" t="s">
         <v>414</v>
       </c>
@@ -8954,7 +8332,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="196" t="s">
         <v>415</v>
       </c>
@@ -8968,7 +8346,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="196" t="s">
         <v>416</v>
       </c>
@@ -8982,7 +8360,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="196" t="s">
         <v>417</v>
       </c>
@@ -8996,7 +8374,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="196" t="s">
         <v>418</v>
       </c>
@@ -9010,7 +8388,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="196" t="s">
         <v>419</v>
       </c>
@@ -9024,7 +8402,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="196" t="s">
         <v>420</v>
       </c>
@@ -9038,7 +8416,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="196" t="s">
         <v>421</v>
       </c>
@@ -9052,7 +8430,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="196" t="s">
         <v>422</v>
       </c>
@@ -9066,7 +8444,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="196" t="s">
         <v>423</v>
       </c>
@@ -9080,7 +8458,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="196" t="s">
         <v>424</v>
       </c>
@@ -9094,7 +8472,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="196" t="s">
         <v>425</v>
       </c>
@@ -9108,7 +8486,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="196" t="s">
         <v>426</v>
       </c>
@@ -9122,7 +8500,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="196" t="s">
         <v>427</v>
       </c>
@@ -9136,7 +8514,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="196" t="s">
         <v>428</v>
       </c>
@@ -9150,7 +8528,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="196" t="s">
         <v>429</v>
       </c>
@@ -9164,7 +8542,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="196" t="s">
         <v>430</v>
       </c>
@@ -9178,7 +8556,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="196" t="s">
         <v>431</v>
       </c>
@@ -9192,7 +8570,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="196" t="s">
         <v>432</v>
       </c>
@@ -9206,7 +8584,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="196" t="s">
         <v>433</v>
       </c>
@@ -9220,7 +8598,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="196" t="s">
         <v>434</v>
       </c>
@@ -9234,7 +8612,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="196" t="s">
         <v>435</v>
       </c>
@@ -9248,7 +8626,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="196" t="s">
         <v>436</v>
       </c>
@@ -9262,7 +8640,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="196" t="s">
         <v>437</v>
       </c>
@@ -9276,7 +8654,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="196" t="s">
         <v>438</v>
       </c>
@@ -9290,7 +8668,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="196" t="s">
         <v>439</v>
       </c>
@@ -9304,7 +8682,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="196" t="s">
         <v>440</v>
       </c>
@@ -9318,7 +8696,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="196" t="s">
         <v>441</v>
       </c>
@@ -9332,7 +8710,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="196" t="s">
         <v>442</v>
       </c>
@@ -9346,7 +8724,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="196" t="s">
         <v>443</v>
       </c>
@@ -9360,7 +8738,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="196" t="s">
         <v>444</v>
       </c>
@@ -9374,7 +8752,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="196" t="s">
         <v>445</v>
       </c>
@@ -9388,7 +8766,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="196" t="s">
         <v>446</v>
       </c>
@@ -9402,7 +8780,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="196" t="s">
         <v>447</v>
       </c>
@@ -9416,7 +8794,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="196" t="s">
         <v>448</v>
       </c>
@@ -9430,7 +8808,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="196" t="s">
         <v>449</v>
       </c>
@@ -9444,7 +8822,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="196" t="s">
         <v>450</v>
       </c>
@@ -9458,7 +8836,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="196" t="s">
         <v>451</v>
       </c>
@@ -9472,7 +8850,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="196" t="s">
         <v>452</v>
       </c>
@@ -9486,7 +8864,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="196" t="s">
         <v>453</v>
       </c>
@@ -9500,7 +8878,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="196" t="s">
         <v>454</v>
       </c>
@@ -9514,7 +8892,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="196" t="s">
         <v>455</v>
       </c>
@@ -9528,7 +8906,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="196" t="s">
         <v>456</v>
       </c>
@@ -9542,7 +8920,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="196" t="s">
         <v>457</v>
       </c>
@@ -9556,7 +8934,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="196" t="s">
         <v>458</v>
       </c>
@@ -9570,7 +8948,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="196" t="s">
         <v>459</v>
       </c>
@@ -9584,7 +8962,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="196" t="s">
         <v>460</v>
       </c>
@@ -9598,7 +8976,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="196" t="s">
         <v>461</v>
       </c>
@@ -9612,7 +8990,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="196" t="s">
         <v>462</v>
       </c>
@@ -9626,7 +9004,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="196" t="s">
         <v>463</v>
       </c>
@@ -9640,7 +9018,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="196" t="s">
         <v>464</v>
       </c>
@@ -9654,7 +9032,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="196" t="s">
         <v>465</v>
       </c>
@@ -9668,7 +9046,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="196" t="s">
         <v>466</v>
       </c>
@@ -9682,7 +9060,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="196" t="s">
         <v>467</v>
       </c>
@@ -9696,7 +9074,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="196" t="s">
         <v>468</v>
       </c>
@@ -9710,7 +9088,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="196" t="s">
         <v>469</v>
       </c>
@@ -9724,7 +9102,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="196" t="s">
         <v>470</v>
       </c>
@@ -9738,7 +9116,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="196" t="s">
         <v>471</v>
       </c>
@@ -9752,7 +9130,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="196" t="s">
         <v>472</v>
       </c>
@@ -9766,7 +9144,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="196" t="s">
         <v>473</v>
       </c>
@@ -9780,7 +9158,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="196" t="s">
         <v>474</v>
       </c>
@@ -9794,7 +9172,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="196" t="s">
         <v>475</v>
       </c>
@@ -9808,7 +9186,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="196" t="s">
         <v>476</v>
       </c>
@@ -9822,7 +9200,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="196" t="s">
         <v>477</v>
       </c>
@@ -9836,7 +9214,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="196" t="s">
         <v>478</v>
       </c>
@@ -9850,7 +9228,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="196" t="s">
         <v>479</v>
       </c>
@@ -9864,7 +9242,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="196" t="s">
         <v>480</v>
       </c>
@@ -9878,7 +9256,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="196" t="s">
         <v>481</v>
       </c>
@@ -9892,7 +9270,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="196" t="s">
         <v>482</v>
       </c>
@@ -9906,7 +9284,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="196" t="s">
         <v>483</v>
       </c>
@@ -9920,7 +9298,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="196" t="s">
         <v>484</v>
       </c>
@@ -9934,7 +9312,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="196" t="s">
         <v>485</v>
       </c>
@@ -9948,7 +9326,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="196" t="s">
         <v>486</v>
       </c>
@@ -9962,7 +9340,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="196" t="s">
         <v>487</v>
       </c>
@@ -9976,7 +9354,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="196" t="s">
         <v>488</v>
       </c>
@@ -9990,7 +9368,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="196" t="s">
         <v>489</v>
       </c>
@@ -10004,7 +9382,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="196" t="s">
         <v>490</v>
       </c>
@@ -10018,7 +9396,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="196" t="s">
         <v>491</v>
       </c>
@@ -10032,7 +9410,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="196" t="s">
         <v>492</v>
       </c>
@@ -10046,7 +9424,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="196" t="s">
         <v>493</v>
       </c>
@@ -10060,7 +9438,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="196" t="s">
         <v>494</v>
       </c>
@@ -10074,7 +9452,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="196" t="s">
         <v>495</v>
       </c>
@@ -10088,7 +9466,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="196" t="s">
         <v>496</v>
       </c>
@@ -10102,7 +9480,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="196" t="s">
         <v>497</v>
       </c>
@@ -10116,7 +9494,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="196" t="s">
         <v>498</v>
       </c>
@@ -10130,7 +9508,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="196" t="s">
         <v>499</v>
       </c>
@@ -10144,7 +9522,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="196" t="s">
         <v>500</v>
       </c>
@@ -10158,7 +9536,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="196" t="s">
         <v>501</v>
       </c>
@@ -10172,7 +9550,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="196" t="s">
         <v>502</v>
       </c>
@@ -10186,7 +9564,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="196" t="s">
         <v>503</v>
       </c>
@@ -10200,7 +9578,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="196" t="s">
         <v>504</v>
       </c>
@@ -10214,7 +9592,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="196" t="s">
         <v>505</v>
       </c>
@@ -10228,7 +9606,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="196" t="s">
         <v>506</v>
       </c>
@@ -10242,7 +9620,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="196" t="s">
         <v>507</v>
       </c>
@@ -10256,7 +9634,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="196" t="s">
         <v>508</v>
       </c>
@@ -10270,7 +9648,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="196" t="s">
         <v>509</v>
       </c>
@@ -10284,7 +9662,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="196" t="s">
         <v>510</v>
       </c>
@@ -10298,7 +9676,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="196" t="s">
         <v>511</v>
       </c>
@@ -10312,7 +9690,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="196" t="s">
         <v>512</v>
       </c>
@@ -10326,7 +9704,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="197" t="s">
         <v>513</v>
       </c>
@@ -10352,7 +9730,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="198" t="s">
         <v>516</v>
       </c>
@@ -10370,7 +9748,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="199" t="s">
         <v>518</v>
       </c>
@@ -10386,7 +9764,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="199" t="s">
         <v>520</v>
       </c>
@@ -10402,7 +9780,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="198" t="s">
         <v>521</v>
       </c>
@@ -10418,7 +9796,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="198" t="s">
         <v>522</v>
       </c>
@@ -10434,7 +9812,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="198" t="s">
         <v>523</v>
       </c>
@@ -10450,7 +9828,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="198" t="s">
         <v>524</v>
       </c>
@@ -10466,7 +9844,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="200" t="s">
         <v>525</v>
       </c>
@@ -10482,7 +9860,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="198" t="s">
         <v>526</v>
       </c>
@@ -10498,7 +9876,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="198" t="s">
         <v>527</v>
       </c>
@@ -10514,7 +9892,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="198" t="s">
         <v>528</v>
       </c>
@@ -10530,7 +9908,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="198" t="s">
         <v>529</v>
       </c>
@@ -10546,7 +9924,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="198" t="s">
         <v>530</v>
       </c>
@@ -10562,7 +9940,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="198" t="s">
         <v>531</v>
       </c>
@@ -10578,7 +9956,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="198" t="s">
         <v>532</v>
       </c>
@@ -10594,7 +9972,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="198" t="s">
         <v>533</v>
       </c>
@@ -10610,7 +9988,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="198" t="s">
         <v>534</v>
       </c>
@@ -10626,7 +10004,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="198" t="s">
         <v>535</v>
       </c>
@@ -10642,7 +10020,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="198" t="s">
         <v>536</v>
       </c>
@@ -10658,7 +10036,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="198" t="s">
         <v>537</v>
       </c>
@@ -10674,7 +10052,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="198" t="s">
         <v>538</v>
       </c>
@@ -10690,7 +10068,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="198" t="s">
         <v>539</v>
       </c>
@@ -10706,7 +10084,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="198" t="s">
         <v>540</v>
       </c>
@@ -10722,7 +10100,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="201" t="s">
         <v>541</v>
       </c>
@@ -10738,7 +10116,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="201" t="s">
         <v>543</v>
       </c>
@@ -10754,7 +10132,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="201" t="s">
         <v>544</v>
       </c>
@@ -10770,7 +10148,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="201" t="s">
         <v>545</v>
       </c>
@@ -10786,7 +10164,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="201" t="s">
         <v>546</v>
       </c>
@@ -10802,7 +10180,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="201" t="s">
         <v>547</v>
       </c>
@@ -10818,7 +10196,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="201" t="s">
         <v>548</v>
       </c>
@@ -10834,7 +10212,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="201" t="s">
         <v>549</v>
       </c>
@@ -10850,7 +10228,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="202" t="s">
         <v>550</v>
       </c>
@@ -10866,7 +10244,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="202" t="s">
         <v>552</v>
       </c>
@@ -10882,7 +10260,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="202" t="s">
         <v>553</v>
       </c>
@@ -10898,7 +10276,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="202" t="s">
         <v>554</v>
       </c>
@@ -10914,7 +10292,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="202" t="s">
         <v>555</v>
       </c>
@@ -10930,7 +10308,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="202" t="s">
         <v>556</v>
       </c>
@@ -10946,7 +10324,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="202" t="s">
         <v>557</v>
       </c>
@@ -10962,7 +10340,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="202" t="s">
         <v>558</v>
       </c>
@@ -10978,7 +10356,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="202" t="s">
         <v>559</v>
       </c>
@@ -10994,7 +10372,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="202" t="s">
         <v>560</v>
       </c>
@@ -11010,7 +10388,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="202" t="s">
         <v>561</v>
       </c>
@@ -11026,7 +10404,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="202" t="s">
         <v>562</v>
       </c>
@@ -11042,7 +10420,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="202" t="s">
         <v>563</v>
       </c>
@@ -11058,7 +10436,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="202" t="s">
         <v>564</v>
       </c>
@@ -11074,7 +10452,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="202" t="s">
         <v>565</v>
       </c>
@@ -11090,7 +10468,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="202" t="s">
         <v>566</v>
       </c>
@@ -11106,7 +10484,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="202" t="s">
         <v>567</v>
       </c>
@@ -11122,7 +10500,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="202" t="s">
         <v>568</v>
       </c>
@@ -11138,7 +10516,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="202" t="s">
         <v>569</v>
       </c>
@@ -11154,7 +10532,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="202" t="s">
         <v>570</v>
       </c>
@@ -11170,7 +10548,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="203" t="s">
         <v>571</v>
       </c>
@@ -11186,7 +10564,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="203" t="s">
         <v>573</v>
       </c>
@@ -11202,7 +10580,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="203" t="s">
         <v>574</v>
       </c>
@@ -11218,7 +10596,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="203" t="s">
         <v>575</v>
       </c>
@@ -11234,7 +10612,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="203" t="s">
         <v>576</v>
       </c>
@@ -11250,7 +10628,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="203" t="s">
         <v>577</v>
       </c>
@@ -11266,7 +10644,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="199" t="s">
         <v>578</v>
       </c>
@@ -11282,7 +10660,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="203" t="s">
         <v>579</v>
       </c>
@@ -11298,7 +10676,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="203" t="s">
         <v>580</v>
       </c>
@@ -11314,7 +10692,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="203" t="s">
         <v>581</v>
       </c>
@@ -11330,7 +10708,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="203" t="s">
         <v>582</v>
       </c>
@@ -11346,7 +10724,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="203" t="s">
         <v>583</v>
       </c>
@@ -11362,7 +10740,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="203" t="s">
         <v>584</v>
       </c>
@@ -11378,7 +10756,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="202" t="s">
         <v>585</v>
       </c>
@@ -11394,7 +10772,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="202" t="s">
         <v>586</v>
       </c>
@@ -11410,7 +10788,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="202" t="s">
         <v>587</v>
       </c>
@@ -11426,7 +10804,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="202" t="s">
         <v>588</v>
       </c>
@@ -11442,7 +10820,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="202" t="s">
         <v>589</v>
       </c>
@@ -11458,7 +10836,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="202" t="s">
         <v>590</v>
       </c>
@@ -11474,7 +10852,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="202" t="s">
         <v>591</v>
       </c>
@@ -11490,7 +10868,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="202" t="s">
         <v>592</v>
       </c>
@@ -11506,7 +10884,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="202" t="s">
         <v>593</v>
       </c>
@@ -11522,7 +10900,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="202" t="s">
         <v>594</v>
       </c>
@@ -11538,7 +10916,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="202" t="s">
         <v>595</v>
       </c>
@@ -11554,7 +10932,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="202" t="s">
         <v>596</v>
       </c>
@@ -11570,7 +10948,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="202" t="s">
         <v>597</v>
       </c>
@@ -11586,7 +10964,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="202" t="s">
         <v>598</v>
       </c>
@@ -11602,7 +10980,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="202" t="s">
         <v>599</v>
       </c>
@@ -11618,7 +10996,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="202" t="s">
         <v>600</v>
       </c>
@@ -11634,7 +11012,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="202" t="s">
         <v>601</v>
       </c>
@@ -11650,7 +11028,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="202" t="s">
         <v>602</v>
       </c>
@@ -11666,7 +11044,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="202" t="s">
         <v>603</v>
       </c>
@@ -11682,7 +11060,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="202" t="s">
         <v>604</v>
       </c>
@@ -11698,7 +11076,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="202" t="s">
         <v>605</v>
       </c>
@@ -11714,7 +11092,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="202" t="s">
         <v>606</v>
       </c>
@@ -11730,7 +11108,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="202" t="s">
         <v>607</v>
       </c>
@@ -11746,7 +11124,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="202" t="s">
         <v>608</v>
       </c>
@@ -11762,7 +11140,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="202" t="s">
         <v>609</v>
       </c>
@@ -11778,7 +11156,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="202" t="s">
         <v>610</v>
       </c>
@@ -11794,7 +11172,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="202" t="s">
         <v>611</v>
       </c>
@@ -11810,7 +11188,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="202" t="s">
         <v>612</v>
       </c>
@@ -11826,7 +11204,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="202" t="s">
         <v>613</v>
       </c>
@@ -11842,7 +11220,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="202" t="s">
         <v>614</v>
       </c>
@@ -11858,7 +11236,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="202" t="s">
         <v>615</v>
       </c>
@@ -11874,7 +11252,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="202" t="s">
         <v>616</v>
       </c>
@@ -11890,7 +11268,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="202" t="s">
         <v>617</v>
       </c>
@@ -11906,7 +11284,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="202" t="s">
         <v>618</v>
       </c>
@@ -11922,7 +11300,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="202" t="s">
         <v>619</v>
       </c>
@@ -11938,7 +11316,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="202" t="s">
         <v>620</v>
       </c>
@@ -11954,7 +11332,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="202" t="s">
         <v>621</v>
       </c>
@@ -11970,7 +11348,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="202" t="s">
         <v>622</v>
       </c>
@@ -11986,7 +11364,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="202" t="s">
         <v>623</v>
       </c>
@@ -12002,7 +11380,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="202" t="s">
         <v>624</v>
       </c>
@@ -12018,7 +11396,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="202" t="s">
         <v>625</v>
       </c>
@@ -12034,7 +11412,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="202" t="s">
         <v>626</v>
       </c>
@@ -12050,7 +11428,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="202" t="s">
         <v>627</v>
       </c>
@@ -12066,7 +11444,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="202" t="s">
         <v>628</v>
       </c>
@@ -12082,7 +11460,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="198" t="s">
         <v>629</v>
       </c>
@@ -12098,7 +11476,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="198" t="s">
         <v>630</v>
       </c>
@@ -12114,7 +11492,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="198" t="s">
         <v>631</v>
       </c>
@@ -12130,7 +11508,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="198" t="s">
         <v>632</v>
       </c>
@@ -12146,7 +11524,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="202" t="s">
         <v>633</v>
       </c>
@@ -12162,7 +11540,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="202" t="s">
         <v>634</v>
       </c>
@@ -12178,7 +11556,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="202" t="s">
         <v>635</v>
       </c>
@@ -12194,7 +11572,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="202" t="s">
         <v>636</v>
       </c>
@@ -12210,7 +11588,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="202" t="s">
         <v>637</v>
       </c>
@@ -12226,7 +11604,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="202" t="s">
         <v>638</v>
       </c>
@@ -12242,7 +11620,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="201" t="s">
         <v>639</v>
       </c>
@@ -12258,7 +11636,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="201" t="s">
         <v>640</v>
       </c>
@@ -12274,7 +11652,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="201" t="s">
         <v>641</v>
       </c>
@@ -12290,7 +11668,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="201" t="s">
         <v>642</v>
       </c>
@@ -12306,7 +11684,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="201" t="s">
         <v>643</v>
       </c>
@@ -12322,7 +11700,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="201" t="s">
         <v>644</v>
       </c>
@@ -12338,7 +11716,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="201" t="s">
         <v>645</v>
       </c>
@@ -12354,7 +11732,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="201" t="s">
         <v>646</v>
       </c>
@@ -12370,7 +11748,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="198" t="s">
         <v>647</v>
       </c>
@@ -12386,7 +11764,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="198" t="s">
         <v>648</v>
       </c>
@@ -12402,7 +11780,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="198" t="s">
         <v>649</v>
       </c>
@@ -12418,7 +11796,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="203" t="s">
         <v>650</v>
       </c>
@@ -12434,7 +11812,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="203" t="s">
         <v>651</v>
       </c>
@@ -12450,7 +11828,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="204" t="s">
         <v>652</v>
       </c>
@@ -12466,7 +11844,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="204" t="s">
         <v>654</v>
       </c>
@@ -12482,7 +11860,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="204" t="s">
         <v>655</v>
       </c>
@@ -12498,7 +11876,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="204" t="s">
         <v>656</v>
       </c>
@@ -12514,7 +11892,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="204" t="s">
         <v>657</v>
       </c>
@@ -12530,7 +11908,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="204" t="s">
         <v>658</v>
       </c>
@@ -12546,7 +11924,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="204" t="s">
         <v>659</v>
       </c>
@@ -12562,7 +11940,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="204" t="s">
         <v>660</v>
       </c>
@@ -12578,7 +11956,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="204" t="s">
         <v>661</v>
       </c>
@@ -12594,7 +11972,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="204" t="s">
         <v>662</v>
       </c>
@@ -12610,7 +11988,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="204" t="s">
         <v>663</v>
       </c>
@@ -12626,7 +12004,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="204" t="s">
         <v>664</v>
       </c>
@@ -12642,7 +12020,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="204" t="s">
         <v>665</v>
       </c>
@@ -12658,7 +12036,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="204" t="s">
         <v>666</v>
       </c>
@@ -12674,7 +12052,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="204" t="s">
         <v>667</v>
       </c>
@@ -12690,7 +12068,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="204" t="s">
         <v>668</v>
       </c>
@@ -12706,7 +12084,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="204" t="s">
         <v>669</v>
       </c>
@@ -12722,7 +12100,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="204" t="s">
         <v>670</v>
       </c>
@@ -12738,7 +12116,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="203" t="s">
         <v>671</v>
       </c>
@@ -12754,7 +12132,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="204" t="s">
         <v>672</v>
       </c>
@@ -12770,7 +12148,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="204" t="s">
         <v>673</v>
       </c>
@@ -12786,7 +12164,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="204" t="s">
         <v>674</v>
       </c>
@@ -12802,7 +12180,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="204" t="s">
         <v>675</v>
       </c>
@@ -12818,7 +12196,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="204" t="s">
         <v>676</v>
       </c>
@@ -12834,7 +12212,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="204" t="s">
         <v>677</v>
       </c>
@@ -12850,7 +12228,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="204" t="s">
         <v>678</v>
       </c>
@@ -12866,7 +12244,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="204" t="s">
         <v>679</v>
       </c>
@@ -12882,7 +12260,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="204" t="s">
         <v>680</v>
       </c>
@@ -12898,7 +12276,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="204" t="s">
         <v>681</v>
       </c>
@@ -12914,7 +12292,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="204" t="s">
         <v>682</v>
       </c>
@@ -12930,7 +12308,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="204" t="s">
         <v>683</v>
       </c>
@@ -12946,7 +12324,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="204" t="s">
         <v>684</v>
       </c>
@@ -12962,7 +12340,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="204" t="s">
         <v>685</v>
       </c>
@@ -12978,7 +12356,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="204" t="s">
         <v>686</v>
       </c>
@@ -12994,7 +12372,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="200" t="s">
         <v>687</v>
       </c>
@@ -13010,7 +12388,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="205" t="s">
         <v>688</v>
       </c>
@@ -13026,7 +12404,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="203" t="s">
         <v>690</v>
       </c>
@@ -13042,7 +12420,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="205" t="s">
         <v>691</v>
       </c>
@@ -13058,7 +12436,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="205" t="s">
         <v>692</v>
       </c>
@@ -13074,7 +12452,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="205" t="s">
         <v>693</v>
       </c>
@@ -13090,7 +12468,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="200" t="s">
         <v>694</v>
       </c>
@@ -13106,7 +12484,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="203" t="s">
         <v>695</v>
       </c>
@@ -13122,7 +12500,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="198" t="s">
         <v>696</v>
       </c>
@@ -13138,7 +12516,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="198" t="s">
         <v>697</v>
       </c>
@@ -13154,7 +12532,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="198" t="s">
         <v>698</v>
       </c>
@@ -13170,7 +12548,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="198" t="s">
         <v>699</v>
       </c>
@@ -13186,7 +12564,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="199" t="s">
         <v>700</v>
       </c>
@@ -13202,7 +12580,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="199" t="s">
         <v>701</v>
       </c>
@@ -13218,7 +12596,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="199" t="s">
         <v>702</v>
       </c>
@@ -13234,7 +12612,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="199" t="s">
         <v>703</v>
       </c>
@@ -13250,7 +12628,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="198" t="s">
         <v>704</v>
       </c>
@@ -13266,7 +12644,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="198" t="s">
         <v>705</v>
       </c>
@@ -13282,7 +12660,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="198" t="s">
         <v>706</v>
       </c>
@@ -13298,7 +12676,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="200" t="s">
         <v>707</v>
       </c>
@@ -13314,7 +12692,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="198" t="s">
         <v>708</v>
       </c>
@@ -13330,7 +12708,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="198" t="s">
         <v>709</v>
       </c>
@@ -13346,7 +12724,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="198" t="s">
         <v>710</v>
       </c>
@@ -13362,7 +12740,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="198" t="s">
         <v>711</v>
       </c>
@@ -13378,7 +12756,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="198" t="s">
         <v>712</v>
       </c>
@@ -13394,7 +12772,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="198" t="s">
         <v>713</v>
       </c>
@@ -13410,7 +12788,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="198" t="s">
         <v>714</v>
       </c>
@@ -13426,7 +12804,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="198" t="s">
         <v>715</v>
       </c>
@@ -13442,7 +12820,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="198" t="s">
         <v>716</v>
       </c>
@@ -13458,7 +12836,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="200" t="s">
         <v>717</v>
       </c>
@@ -13474,7 +12852,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="205" t="s">
         <v>718</v>
       </c>
@@ -13490,7 +12868,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="205" t="s">
         <v>719</v>
       </c>
@@ -13506,7 +12884,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="205" t="s">
         <v>720</v>
       </c>
@@ -13522,7 +12900,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="205" t="s">
         <v>721</v>
       </c>
@@ -13538,7 +12916,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="205" t="s">
         <v>722</v>
       </c>
@@ -13570,7 +12948,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="206" t="s">
         <v>724</v>
       </c>
@@ -13586,7 +12964,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="206" t="s">
         <v>726</v>
       </c>
@@ -13602,7 +12980,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="206" t="s">
         <v>727</v>
       </c>
@@ -13618,7 +12996,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="206" t="s">
         <v>728</v>
       </c>
@@ -13634,7 +13012,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="206" t="s">
         <v>729</v>
       </c>
@@ -13650,7 +13028,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="206" t="s">
         <v>730</v>
       </c>
@@ -13666,7 +13044,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="206" t="s">
         <v>731</v>
       </c>
@@ -13682,7 +13060,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="206" t="s">
         <v>732</v>
       </c>
@@ -13698,7 +13076,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="206" t="s">
         <v>733</v>
       </c>
@@ -13714,7 +13092,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="206" t="s">
         <v>734</v>
       </c>
@@ -13730,7 +13108,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="206" t="s">
         <v>735</v>
       </c>
@@ -13746,7 +13124,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="206" t="s">
         <v>736</v>
       </c>
@@ -13762,7 +13140,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="206" t="s">
         <v>737</v>
       </c>
@@ -13778,7 +13156,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="206" t="s">
         <v>738</v>
       </c>
@@ -13794,7 +13172,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="206" t="s">
         <v>739</v>
       </c>
@@ -13810,7 +13188,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" s="201" t="s">
         <v>740</v>
       </c>
@@ -13826,7 +13204,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="201" t="s">
         <v>741</v>
       </c>
@@ -13842,7 +13220,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="201" t="s">
         <v>742</v>
       </c>
@@ -13858,7 +13236,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="201" t="s">
         <v>743</v>
       </c>
@@ -13874,7 +13252,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="201" t="s">
         <v>744</v>
       </c>
@@ -13890,7 +13268,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="201" t="s">
         <v>745</v>
       </c>
@@ -13906,7 +13284,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="201" t="s">
         <v>746</v>
       </c>
@@ -13922,7 +13300,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="201" t="s">
         <v>747</v>
       </c>
@@ -13938,7 +13316,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="201" t="s">
         <v>748</v>
       </c>
@@ -13954,7 +13332,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="201" t="s">
         <v>749</v>
       </c>
@@ -13970,7 +13348,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="201" t="s">
         <v>750</v>
       </c>
@@ -13986,7 +13364,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="201" t="s">
         <v>751</v>
       </c>
@@ -14002,7 +13380,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="201" t="s">
         <v>752</v>
       </c>
@@ -14018,7 +13396,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="201" t="s">
         <v>753</v>
       </c>
@@ -14034,7 +13412,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="201" t="s">
         <v>754</v>
       </c>
@@ -14050,7 +13428,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="201" t="s">
         <v>755</v>
       </c>
@@ -14066,7 +13444,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="201" t="s">
         <v>756</v>
       </c>
@@ -14082,7 +13460,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="201" t="s">
         <v>757</v>
       </c>
@@ -14098,7 +13476,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="201" t="s">
         <v>758</v>
       </c>
@@ -14114,7 +13492,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="201" t="s">
         <v>759</v>
       </c>
@@ -14130,7 +13508,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" s="201" t="s">
         <v>760</v>
       </c>
@@ -14146,7 +13524,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" s="201" t="s">
         <v>761</v>
       </c>
@@ -14162,7 +13540,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" s="201" t="s">
         <v>762</v>
       </c>
@@ -14178,7 +13556,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" s="201" t="s">
         <v>763</v>
       </c>
@@ -14194,7 +13572,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="201" t="s">
         <v>764</v>
       </c>
@@ -14210,7 +13588,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="201" t="s">
         <v>765</v>
       </c>
@@ -14226,7 +13604,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="201" t="s">
         <v>766</v>
       </c>
@@ -14242,7 +13620,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="201" t="s">
         <v>767</v>
       </c>
@@ -14258,7 +13636,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="201" t="s">
         <v>768</v>
       </c>
@@ -14274,7 +13652,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="201" t="s">
         <v>769</v>
       </c>
@@ -14290,7 +13668,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" s="201" t="s">
         <v>770</v>
       </c>
@@ -14306,7 +13684,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="201" t="s">
         <v>771</v>
       </c>
@@ -14322,7 +13700,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="201" t="s">
         <v>772</v>
       </c>
@@ -14338,7 +13716,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" s="201" t="s">
         <v>773</v>
       </c>
@@ -14354,7 +13732,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="201" t="s">
         <v>774</v>
       </c>
@@ -14370,7 +13748,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="201" t="s">
         <v>775</v>
       </c>
@@ -14386,7 +13764,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" s="205" t="s">
         <v>776</v>
       </c>
@@ -14402,7 +13780,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" s="205" t="s">
         <v>777</v>
       </c>
@@ -14418,7 +13796,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" s="205" t="s">
         <v>778</v>
       </c>
@@ -14434,7 +13812,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="205" t="s">
         <v>779</v>
       </c>
@@ -14450,7 +13828,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="205" t="s">
         <v>780</v>
       </c>
@@ -14466,7 +13844,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="198" t="s">
         <v>781</v>
       </c>
@@ -14482,7 +13860,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="198" t="s">
         <v>782</v>
       </c>
@@ -14498,7 +13876,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="198" t="s">
         <v>783</v>
       </c>
@@ -14514,7 +13892,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="198" t="s">
         <v>784</v>
       </c>
@@ -14530,7 +13908,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="198" t="s">
         <v>785</v>
       </c>
@@ -14546,7 +13924,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="198" t="s">
         <v>786</v>
       </c>
@@ -14562,7 +13940,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="198" t="s">
         <v>787</v>
       </c>
@@ -14578,7 +13956,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="200" t="s">
         <v>788</v>
       </c>
@@ -14594,7 +13972,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="205" t="s">
         <v>789</v>
       </c>
@@ -14610,7 +13988,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="205" t="s">
         <v>790</v>
       </c>
@@ -14626,7 +14004,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="205" t="s">
         <v>791</v>
       </c>
@@ -14642,7 +14020,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="198" t="s">
         <v>792</v>
       </c>
@@ -14658,7 +14036,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="198" t="s">
         <v>793</v>
       </c>
@@ -14674,7 +14052,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="198" t="s">
         <v>794</v>
       </c>
@@ -14690,7 +14068,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="198" t="s">
         <v>795</v>
       </c>
@@ -14706,7 +14084,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="198" t="s">
         <v>796</v>
       </c>
@@ -14722,7 +14100,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="198" t="s">
         <v>797</v>
       </c>
@@ -14738,7 +14116,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="198" t="s">
         <v>798</v>
       </c>
@@ -14754,7 +14132,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="198" t="s">
         <v>799</v>
       </c>
@@ -14770,7 +14148,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="198" t="s">
         <v>800</v>
       </c>
@@ -14786,7 +14164,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="198" t="s">
         <v>801</v>
       </c>
@@ -14802,7 +14180,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="198" t="s">
         <v>802</v>
       </c>
@@ -14818,7 +14196,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="198" t="s">
         <v>803</v>
       </c>
@@ -14834,7 +14212,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="200" t="s">
         <v>804</v>
       </c>
@@ -14850,7 +14228,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="201" t="s">
         <v>805</v>
       </c>
@@ -14866,7 +14244,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="201" t="s">
         <v>806</v>
       </c>
@@ -14882,7 +14260,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="201" t="s">
         <v>807</v>
       </c>
@@ -14898,7 +14276,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="201" t="s">
         <v>808</v>
       </c>
@@ -14914,7 +14292,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="201" t="s">
         <v>809</v>
       </c>
@@ -14930,7 +14308,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="201" t="s">
         <v>810</v>
       </c>
@@ -14946,7 +14324,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" s="201" t="s">
         <v>811</v>
       </c>
@@ -14962,7 +14340,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" s="201" t="s">
         <v>812</v>
       </c>
@@ -14978,7 +14356,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" s="199" t="s">
         <v>813</v>
       </c>
@@ -14994,7 +14372,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="199" t="s">
         <v>814</v>
       </c>
@@ -15010,7 +14388,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" s="199" t="s">
         <v>815</v>
       </c>
@@ -15026,7 +14404,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="198" t="s">
         <v>816</v>
       </c>
@@ -15044,7 +14422,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" s="199" t="s">
         <v>817</v>
       </c>
@@ -15060,7 +14438,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" s="201" t="s">
         <v>818</v>
       </c>
@@ -15076,7 +14454,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" s="201" t="s">
         <v>819</v>
       </c>
@@ -15092,7 +14470,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" s="201" t="s">
         <v>820</v>
       </c>
@@ -15108,7 +14486,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" s="201" t="s">
         <v>821</v>
       </c>
@@ -15124,7 +14502,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" s="202" t="s">
         <v>822</v>
       </c>
@@ -15140,7 +14518,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" s="202" t="s">
         <v>823</v>
       </c>
@@ -15156,7 +14534,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" s="202" t="s">
         <v>824</v>
       </c>
@@ -15172,7 +14550,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" s="202" t="s">
         <v>825</v>
       </c>
@@ -15188,7 +14566,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A499" s="202" t="s">
         <v>826</v>
       </c>
@@ -15204,7 +14582,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A500" s="202" t="s">
         <v>827</v>
       </c>
@@ -15220,7 +14598,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A501" s="202" t="s">
         <v>828</v>
       </c>
@@ -15236,7 +14614,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A502" s="202" t="s">
         <v>829</v>
       </c>
@@ -15252,7 +14630,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A503" s="199" t="s">
         <v>830</v>
       </c>
@@ -15268,7 +14646,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A504" s="199" t="s">
         <v>831</v>
       </c>
@@ -15284,7 +14662,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A505" s="198" t="s">
         <v>832</v>
       </c>
@@ -15300,7 +14678,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A506" s="202" t="s">
         <v>833</v>
       </c>
@@ -15316,7 +14694,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A507" s="202" t="s">
         <v>834</v>
       </c>
@@ -15332,7 +14710,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A508" s="202" t="s">
         <v>835</v>
       </c>
@@ -15348,7 +14726,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A509" s="202" t="s">
         <v>836</v>
       </c>
@@ -15364,7 +14742,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A510" s="202" t="s">
         <v>837</v>
       </c>
@@ -15380,7 +14758,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A511" s="202" t="s">
         <v>838</v>
       </c>
@@ -15396,7 +14774,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" s="202" t="s">
         <v>839</v>
       </c>
@@ -15412,7 +14790,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" s="202" t="s">
         <v>840</v>
       </c>
@@ -15428,7 +14806,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" s="202" t="s">
         <v>841</v>
       </c>
@@ -15444,7 +14822,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" s="202" t="s">
         <v>842</v>
       </c>
@@ -15460,7 +14838,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" s="202" t="s">
         <v>843</v>
       </c>
@@ -15476,7 +14854,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" s="202" t="s">
         <v>844</v>
       </c>
@@ -15492,7 +14870,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" s="202" t="s">
         <v>845</v>
       </c>
@@ -15508,7 +14886,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" s="202" t="s">
         <v>846</v>
       </c>
@@ -15524,7 +14902,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" s="202" t="s">
         <v>847</v>
       </c>
@@ -15540,7 +14918,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" s="202" t="s">
         <v>848</v>
       </c>
@@ -15556,7 +14934,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" s="202" t="s">
         <v>849</v>
       </c>
@@ -15572,7 +14950,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" s="202" t="s">
         <v>850</v>
       </c>
@@ -15588,7 +14966,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" s="202" t="s">
         <v>851</v>
       </c>
@@ -15604,7 +14982,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" s="202" t="s">
         <v>852</v>
       </c>
@@ -15620,7 +14998,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" s="202" t="s">
         <v>853</v>
       </c>
@@ -15636,7 +15014,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" s="202" t="s">
         <v>854</v>
       </c>
@@ -15652,7 +15030,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" s="201" t="s">
         <v>855</v>
       </c>
@@ -15668,7 +15046,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" s="201" t="s">
         <v>856</v>
       </c>
@@ -15684,7 +15062,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" s="201" t="s">
         <v>857</v>
       </c>
@@ -15700,7 +15078,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" s="201" t="s">
         <v>858</v>
       </c>
@@ -15716,7 +15094,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" s="201" t="s">
         <v>859</v>
       </c>
@@ -15732,7 +15110,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" s="201" t="s">
         <v>860</v>
       </c>
@@ -15748,7 +15126,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" s="201" t="s">
         <v>861</v>
       </c>
@@ -15764,7 +15142,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" s="201" t="s">
         <v>862</v>
       </c>
@@ -15780,7 +15158,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" s="201" t="s">
         <v>863</v>
       </c>
@@ -15796,7 +15174,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" s="201" t="s">
         <v>864</v>
       </c>
@@ -15812,7 +15190,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" s="201" t="s">
         <v>865</v>
       </c>
@@ -15828,7 +15206,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" s="201" t="s">
         <v>866</v>
       </c>
@@ -15844,7 +15222,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" s="201" t="s">
         <v>867</v>
       </c>
@@ -15860,7 +15238,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" s="201" t="s">
         <v>868</v>
       </c>
@@ -15876,7 +15254,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" s="201" t="s">
         <v>869</v>
       </c>
@@ -15892,7 +15270,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" s="201" t="s">
         <v>870</v>
       </c>
@@ -15908,7 +15286,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" s="201" t="s">
         <v>871</v>
       </c>
@@ -15924,7 +15302,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" s="201" t="s">
         <v>872</v>
       </c>
@@ -15940,7 +15318,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" s="201" t="s">
         <v>873</v>
       </c>
@@ -15956,7 +15334,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" s="201" t="s">
         <v>874</v>
       </c>
@@ -15972,7 +15350,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" s="201" t="s">
         <v>875</v>
       </c>
@@ -15988,7 +15366,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" s="201" t="s">
         <v>876</v>
       </c>
@@ -16004,7 +15382,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" s="201" t="s">
         <v>877</v>
       </c>
@@ -16020,7 +15398,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" s="201" t="s">
         <v>878</v>
       </c>
@@ -16036,7 +15414,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" s="201" t="s">
         <v>879</v>
       </c>
@@ -16052,7 +15430,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" s="201" t="s">
         <v>880</v>
       </c>
@@ -16068,7 +15446,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" s="201" t="s">
         <v>881</v>
       </c>
@@ -16084,7 +15462,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" s="201" t="s">
         <v>882</v>
       </c>
@@ -16100,7 +15478,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="201" t="s">
         <v>883</v>
       </c>
@@ -16116,7 +15494,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="201" t="s">
         <v>884</v>
       </c>
@@ -16132,7 +15510,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="201" t="s">
         <v>885</v>
       </c>
@@ -16148,7 +15526,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="201" t="s">
         <v>886</v>
       </c>
@@ -16164,7 +15542,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A560" s="201" t="s">
         <v>887</v>
       </c>
@@ -16180,7 +15558,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A561" s="201" t="s">
         <v>888</v>
       </c>
@@ -16196,7 +15574,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A562" s="201" t="s">
         <v>889</v>
       </c>
@@ -16212,7 +15590,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A563" s="201" t="s">
         <v>890</v>
       </c>
@@ -16228,7 +15606,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A564" s="201" t="s">
         <v>891</v>
       </c>
@@ -16244,7 +15622,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A565" s="201" t="s">
         <v>892</v>
       </c>
@@ -16260,7 +15638,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A566" s="201" t="s">
         <v>893</v>
       </c>
@@ -16276,7 +15654,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A567" s="201" t="s">
         <v>894</v>
       </c>
@@ -16292,7 +15670,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A568" s="201" t="s">
         <v>895</v>
       </c>
@@ -16308,7 +15686,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A569" s="201" t="s">
         <v>896</v>
       </c>
@@ -16324,7 +15702,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A570" s="201" t="s">
         <v>897</v>
       </c>
@@ -16340,7 +15718,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A571" s="201" t="s">
         <v>898</v>
       </c>
@@ -16356,7 +15734,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" s="201" t="s">
         <v>899</v>
       </c>
@@ -16372,7 +15750,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" s="199" t="s">
         <v>900</v>
       </c>
@@ -16388,7 +15766,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" s="198" t="s">
         <v>901</v>
       </c>
@@ -16404,7 +15782,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" s="198" t="s">
         <v>902</v>
       </c>
@@ -16420,7 +15798,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" s="198" t="s">
         <v>903</v>
       </c>
@@ -16436,7 +15814,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" s="198" t="s">
         <v>904</v>
       </c>
@@ -16452,7 +15830,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" s="198" t="s">
         <v>905</v>
       </c>
@@ -16468,7 +15846,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" s="198" t="s">
         <v>906</v>
       </c>
@@ -16484,7 +15862,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" s="198" t="s">
         <v>907</v>
       </c>
@@ -16500,7 +15878,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" s="198" t="s">
         <v>908</v>
       </c>
@@ -16516,7 +15894,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" s="198" t="s">
         <v>909</v>
       </c>
@@ -16532,7 +15910,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" s="198" t="s">
         <v>910</v>
       </c>
@@ -16548,7 +15926,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" s="198" t="s">
         <v>911</v>
       </c>
@@ -16564,7 +15942,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" s="198" t="s">
         <v>912</v>
       </c>
@@ -16580,7 +15958,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" s="198" t="s">
         <v>913</v>
       </c>
@@ -16596,7 +15974,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" s="198" t="s">
         <v>914</v>
       </c>
@@ -16612,7 +15990,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" s="200" t="s">
         <v>915</v>
       </c>
@@ -16628,7 +16006,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" s="198" t="s">
         <v>916</v>
       </c>
@@ -16646,7 +16024,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" s="199" t="s">
         <v>917</v>
       </c>
@@ -16662,7 +16040,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" s="199" t="s">
         <v>918</v>
       </c>
@@ -16678,7 +16056,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A592" s="199" t="s">
         <v>919</v>
       </c>
@@ -16694,7 +16072,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A593" s="203" t="s">
         <v>920</v>
       </c>
@@ -16710,7 +16088,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A594" s="200" t="s">
         <v>921</v>
       </c>
@@ -16726,7 +16104,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A595" s="200" t="s">
         <v>922</v>
       </c>
@@ -16742,7 +16120,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A596" s="200" t="s">
         <v>923</v>
       </c>
@@ -16758,7 +16136,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A597" s="200" t="s">
         <v>924</v>
       </c>
@@ -16774,7 +16152,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A598" s="200" t="s">
         <v>925</v>
       </c>
@@ -16790,7 +16168,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A599" s="200" t="s">
         <v>926</v>
       </c>
@@ -16806,7 +16184,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A600" s="199" t="s">
         <v>927</v>
       </c>
@@ -16822,7 +16200,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A601" s="205" t="s">
         <v>928</v>
       </c>
@@ -16838,7 +16216,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A602" s="205" t="s">
         <v>929</v>
       </c>
@@ -16854,7 +16232,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A603" s="205" t="s">
         <v>930</v>
       </c>
@@ -16870,7 +16248,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A604" s="205" t="s">
         <v>931</v>
       </c>
@@ -16886,7 +16264,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A605" s="205" t="s">
         <v>932</v>
       </c>
@@ -16902,7 +16280,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A606" s="205" t="s">
         <v>933</v>
       </c>
@@ -16918,7 +16296,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A607" s="202" t="s">
         <v>934</v>
       </c>
@@ -16934,7 +16312,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A608" s="202" t="s">
         <v>935</v>
       </c>
@@ -16950,7 +16328,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A609" s="202" t="s">
         <v>936</v>
       </c>
@@ -16966,7 +16344,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A610" s="202" t="s">
         <v>937</v>
       </c>
@@ -16982,7 +16360,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A611" s="202" t="s">
         <v>938</v>
       </c>
@@ -16998,7 +16376,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A612" s="202" t="s">
         <v>939</v>
       </c>
@@ -17014,7 +16392,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A613" s="202" t="s">
         <v>940</v>
       </c>
@@ -17030,7 +16408,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A614" s="202" t="s">
         <v>941</v>
       </c>
@@ -17046,7 +16424,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A615" s="202" t="s">
         <v>942</v>
       </c>
@@ -17062,7 +16440,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A616" s="201" t="s">
         <v>943</v>
       </c>
@@ -17078,7 +16456,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A617" s="201" t="s">
         <v>944</v>
       </c>
@@ -17094,7 +16472,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A618" s="201" t="s">
         <v>945</v>
       </c>
@@ -17110,7 +16488,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A619" s="201" t="s">
         <v>946</v>
       </c>
@@ -17126,7 +16504,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A620" s="201" t="s">
         <v>947</v>
       </c>
@@ -17142,7 +16520,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A621" s="201" t="s">
         <v>948</v>
       </c>
@@ -17158,7 +16536,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A622" s="201" t="s">
         <v>949</v>
       </c>
@@ -17174,7 +16552,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A623" s="201" t="s">
         <v>950</v>
       </c>
@@ -17190,7 +16568,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A624" s="201" t="s">
         <v>951</v>
       </c>
@@ -17206,7 +16584,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A625" s="201" t="s">
         <v>952</v>
       </c>
@@ -17222,7 +16600,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A626" s="201" t="s">
         <v>953</v>
       </c>
@@ -17238,7 +16616,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A627" s="201" t="s">
         <v>954</v>
       </c>
@@ -17254,7 +16632,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A628" s="201" t="s">
         <v>955</v>
       </c>
@@ -17270,7 +16648,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A629" s="201" t="s">
         <v>956</v>
       </c>
@@ -17286,7 +16664,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A630" s="201" t="s">
         <v>957</v>
       </c>
@@ -17302,7 +16680,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A631" s="201" t="s">
         <v>958</v>
       </c>
@@ -17318,7 +16696,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A632" s="201" t="s">
         <v>959</v>
       </c>
@@ -17334,7 +16712,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A633" s="201" t="s">
         <v>960</v>
       </c>
@@ -17350,7 +16728,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A634" s="202" t="s">
         <v>961</v>
       </c>
@@ -17366,7 +16744,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A635" s="202" t="s">
         <v>962</v>
       </c>
@@ -17382,7 +16760,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A636" s="202" t="s">
         <v>963</v>
       </c>
@@ -17398,7 +16776,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A637" s="202" t="s">
         <v>964</v>
       </c>
@@ -17414,7 +16792,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A638" s="202" t="s">
         <v>965</v>
       </c>
@@ -17430,7 +16808,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A639" s="202" t="s">
         <v>966</v>
       </c>
@@ -17446,7 +16824,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A640" s="202" t="s">
         <v>967</v>
       </c>
@@ -17462,7 +16840,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A641" s="202" t="s">
         <v>968</v>
       </c>
@@ -17478,7 +16856,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A642" s="202" t="s">
         <v>969</v>
       </c>
@@ -17494,7 +16872,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A643" s="202" t="s">
         <v>970</v>
       </c>
@@ -17510,7 +16888,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A644" s="202" t="s">
         <v>971</v>
       </c>
@@ -17526,7 +16904,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A645" s="201" t="s">
         <v>972</v>
       </c>
@@ -17542,7 +16920,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A646" s="201" t="s">
         <v>973</v>
       </c>
@@ -17558,7 +16936,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A647" s="201" t="s">
         <v>974</v>
       </c>
@@ -17574,7 +16952,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A648" s="201" t="s">
         <v>975</v>
       </c>
@@ -17590,7 +16968,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A649" s="201" t="s">
         <v>976</v>
       </c>
@@ -17606,7 +16984,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A650" s="201" t="s">
         <v>977</v>
       </c>
@@ -17622,7 +17000,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A651" s="201" t="s">
         <v>978</v>
       </c>
@@ -17638,7 +17016,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A652" s="201" t="s">
         <v>979</v>
       </c>
@@ -17654,7 +17032,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A653" s="201" t="s">
         <v>980</v>
       </c>
@@ -17670,7 +17048,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A654" s="201" t="s">
         <v>981</v>
       </c>
@@ -17686,7 +17064,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A655" s="201" t="s">
         <v>982</v>
       </c>
@@ -17702,7 +17080,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A656" s="201" t="s">
         <v>983</v>
       </c>
@@ -17718,7 +17096,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A657" s="201" t="s">
         <v>984</v>
       </c>
@@ -17734,7 +17112,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A658" s="201" t="s">
         <v>985</v>
       </c>
@@ -17750,7 +17128,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A659" s="201" t="s">
         <v>986</v>
       </c>
@@ -17766,7 +17144,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A660" s="201" t="s">
         <v>987</v>
       </c>
@@ -17782,7 +17160,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A661" s="201" t="s">
         <v>988</v>
       </c>
@@ -17798,7 +17176,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A662" s="201" t="s">
         <v>989</v>
       </c>
@@ -17814,7 +17192,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A663" s="201" t="s">
         <v>990</v>
       </c>
@@ -17830,7 +17208,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A664" s="201" t="s">
         <v>991</v>
       </c>
@@ -17846,7 +17224,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A665" s="201" t="s">
         <v>992</v>
       </c>
@@ -17862,7 +17240,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A666" s="201" t="s">
         <v>993</v>
       </c>
@@ -17878,7 +17256,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A667" s="201" t="s">
         <v>994</v>
       </c>
@@ -17894,7 +17272,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A668" s="201" t="s">
         <v>995</v>
       </c>
@@ -17910,7 +17288,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A669" s="201" t="s">
         <v>996</v>
       </c>
@@ -17926,7 +17304,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A670" s="201" t="s">
         <v>997</v>
       </c>
@@ -17942,7 +17320,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A671" s="201" t="s">
         <v>998</v>
       </c>
@@ -17958,7 +17336,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A672" s="201" t="s">
         <v>999</v>
       </c>
@@ -17974,7 +17352,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A673" s="201" t="s">
         <v>1000</v>
       </c>
@@ -17990,7 +17368,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A674" s="201" t="s">
         <v>1001</v>
       </c>
@@ -18006,7 +17384,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A675" s="201" t="s">
         <v>1002</v>
       </c>
@@ -18022,7 +17400,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A676" s="201" t="s">
         <v>1003</v>
       </c>
@@ -18038,7 +17416,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A677" s="201" t="s">
         <v>1004</v>
       </c>
@@ -18054,7 +17432,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A678" s="201" t="s">
         <v>1005</v>
       </c>
@@ -18070,7 +17448,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A679" s="201" t="s">
         <v>1006</v>
       </c>
@@ -18086,7 +17464,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A680" s="201" t="s">
         <v>1007</v>
       </c>
@@ -18102,7 +17480,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A681" s="201" t="s">
         <v>1008</v>
       </c>
@@ -18118,7 +17496,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A682" s="201" t="s">
         <v>1009</v>
       </c>
@@ -18134,7 +17512,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A683" s="201" t="s">
         <v>1010</v>
       </c>
@@ -18150,7 +17528,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A684" s="201" t="s">
         <v>1011</v>
       </c>
@@ -18166,7 +17544,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A685" s="201" t="s">
         <v>1012</v>
       </c>
@@ -18182,7 +17560,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A686" s="201" t="s">
         <v>1013</v>
       </c>
@@ -18198,7 +17576,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A687" s="201" t="s">
         <v>1014</v>
       </c>
@@ -18214,7 +17592,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A688" s="201" t="s">
         <v>1015</v>
       </c>
@@ -18230,7 +17608,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A689" s="201" t="s">
         <v>1016</v>
       </c>
@@ -18246,7 +17624,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A690" s="203" t="s">
         <v>1017</v>
       </c>
@@ -18262,7 +17640,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A691" s="198" t="s">
         <v>1018</v>
       </c>
@@ -18279,18 +17657,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H691" xr:uid="{00000000-0009-0000-0000-00000A000000}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="ELECTRICITY"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H691" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FFEC5561"/>
@@ -18345,7 +17717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -18408,7 +17780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
@@ -36579,10 +35951,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
-    <tabColor theme="7" tint="0.59999389629810485"/>
+    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
   </sheetPr>
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -37004,7 +36376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor theme="2" tint="-9.9978637043366805E-2"/>
@@ -38010,7 +37382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -40311,7 +39683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.14999847407452621"/>
@@ -40959,10 +40331,726 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
+  </sheetPr>
+  <dimension ref="A1:S30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="100" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="45">
+        <v>71300</v>
+      </c>
+      <c r="C3" s="45">
+        <v>110658</v>
+      </c>
+      <c r="D3" s="45">
+        <v>127302</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="45">
+        <v>0</v>
+      </c>
+      <c r="C4" s="45">
+        <v>12789</v>
+      </c>
+      <c r="D4" s="45">
+        <v>11850</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>300</v>
+      </c>
+      <c r="C5" s="9">
+        <v>320</v>
+      </c>
+      <c r="D5" s="9">
+        <v>310</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="45">
+        <v>902171.34</v>
+      </c>
+      <c r="C6" s="45">
+        <v>902171.34</v>
+      </c>
+      <c r="D6" s="45">
+        <v>902171.34</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="9">
+        <v>100</v>
+      </c>
+      <c r="C7" s="9">
+        <v>100</v>
+      </c>
+      <c r="D7" s="9">
+        <v>100</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="10" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="123" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="124" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="125" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="126" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="124" t="s">
+        <v>187</v>
+      </c>
+      <c r="J11" s="125" t="s">
+        <v>188</v>
+      </c>
+      <c r="K11" s="126" t="s">
+        <v>189</v>
+      </c>
+      <c r="L11" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="M11" s="124" t="s">
+        <v>191</v>
+      </c>
+      <c r="N11" s="94" t="s">
+        <v>192</v>
+      </c>
+      <c r="O11" s="123" t="s">
+        <v>62</v>
+      </c>
+      <c r="P11" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="R11" s="94"/>
+      <c r="S11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="128" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="129">
+        <v>0</v>
+      </c>
+      <c r="C12" s="130">
+        <v>132.1138129435102</v>
+      </c>
+      <c r="D12" s="29">
+        <v>334.5549512355899</v>
+      </c>
+      <c r="E12" s="79">
+        <v>301.5706207743001</v>
+      </c>
+      <c r="F12" s="79">
+        <v>212.0418932866599</v>
+      </c>
+      <c r="G12" s="79">
+        <v>179.0575628253699</v>
+      </c>
+      <c r="H12" s="131">
+        <v>84.816757314669871</v>
+      </c>
+      <c r="I12" s="129">
+        <v>0</v>
+      </c>
+      <c r="J12" s="130">
+        <v>105.6910503548001</v>
+      </c>
+      <c r="K12" s="29">
+        <v>105.6910503548001</v>
+      </c>
+      <c r="L12" s="131">
+        <f>105.6910503548+0.147</f>
+        <v>105.8380503548</v>
+      </c>
+      <c r="M12" s="129">
+        <v>0</v>
+      </c>
+      <c r="N12" s="132">
+        <v>0</v>
+      </c>
+      <c r="O12" s="129" t="s">
+        <v>194</v>
+      </c>
+      <c r="P12" s="129" t="s">
+        <v>195</v>
+      </c>
+      <c r="R12" s="93"/>
+      <c r="S12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="133" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="26">
+        <v>440.37930928179981</v>
+      </c>
+      <c r="C13" s="134">
+        <v>317.07315106442002</v>
+      </c>
+      <c r="D13" s="8">
+        <v>317.07315106441979</v>
+      </c>
+      <c r="E13" s="9">
+        <v>317.07315106441979</v>
+      </c>
+      <c r="F13" s="9">
+        <v>317.07315106441979</v>
+      </c>
+      <c r="G13" s="9">
+        <v>317.07315106441979</v>
+      </c>
+      <c r="H13" s="14">
+        <v>317.07315106441979</v>
+      </c>
+      <c r="I13" s="26">
+        <v>484.41738132276009</v>
+      </c>
+      <c r="J13" s="134">
+        <v>264.22762588702</v>
+      </c>
+      <c r="K13" s="8">
+        <v>264.22762588702</v>
+      </c>
+      <c r="L13" s="14">
+        <v>264.22762588702</v>
+      </c>
+      <c r="M13" s="26">
+        <v>493.22483445920028</v>
+      </c>
+      <c r="N13" s="30">
+        <v>0</v>
+      </c>
+      <c r="O13" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="P13" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="26">
+        <v>598.9160864036869</v>
+      </c>
+      <c r="C14" s="134">
+        <v>607.72374112982209</v>
+      </c>
+      <c r="D14" s="8">
+        <v>654.97377625205797</v>
+      </c>
+      <c r="E14" s="9">
+        <v>631.41349398681803</v>
+      </c>
+      <c r="F14" s="9">
+        <v>654.97377625205797</v>
+      </c>
+      <c r="G14" s="9">
+        <v>560.732862891266</v>
+      </c>
+      <c r="H14" s="14">
+        <v>518.32448423393498</v>
+      </c>
+      <c r="I14" s="26">
+        <v>519.64759704790811</v>
+      </c>
+      <c r="J14" s="134">
+        <v>572.49332381499198</v>
+      </c>
+      <c r="K14" s="135">
+        <v>572.49332381499198</v>
+      </c>
+      <c r="L14" s="136">
+        <v>572.49332381499198</v>
+      </c>
+      <c r="M14" s="26">
+        <v>510.8399423217781</v>
+      </c>
+      <c r="N14" s="30">
+        <v>0</v>
+      </c>
+      <c r="O14" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="26">
+        <v>1277.1002589838199</v>
+      </c>
+      <c r="C15" s="134">
+        <v>158.53657553220989</v>
+      </c>
+      <c r="D15" s="8">
+        <v>306.28280664744801</v>
+      </c>
+      <c r="E15" s="9">
+        <v>282.72252438220801</v>
+      </c>
+      <c r="F15" s="9">
+        <v>193.19379689456511</v>
+      </c>
+      <c r="G15" s="9">
+        <v>169.63351462932499</v>
+      </c>
+      <c r="H15" s="14">
+        <v>80.10478714168201</v>
+      </c>
+      <c r="I15" s="26">
+        <v>317.07315106442002</v>
+      </c>
+      <c r="J15" s="134">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0</v>
+      </c>
+      <c r="M15" s="26">
+        <v>0</v>
+      </c>
+      <c r="N15" s="30">
+        <v>554.87801436273696</v>
+      </c>
+      <c r="O15" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="P15" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="96">
+        <v>0</v>
+      </c>
+      <c r="C16" s="97">
+        <v>563.68566908885987</v>
+      </c>
+      <c r="D16" s="88">
+        <v>339.26702925864407</v>
+      </c>
+      <c r="E16" s="89">
+        <v>400.52372000823402</v>
+      </c>
+      <c r="F16" s="89">
+        <v>513.61251406094698</v>
+      </c>
+      <c r="G16" s="89">
+        <v>527.74885598022911</v>
+      </c>
+      <c r="H16" s="98">
+        <v>654.97388410213307</v>
+      </c>
+      <c r="I16" s="96">
+        <v>0</v>
+      </c>
+      <c r="J16" s="97">
+        <v>704.60713675850002</v>
+      </c>
+      <c r="K16" s="88">
+        <v>735.07856339373586</v>
+      </c>
+      <c r="L16" s="98">
+        <v>673.82208834431788</v>
+      </c>
+      <c r="M16" s="96">
+        <v>0</v>
+      </c>
+      <c r="N16" s="99">
+        <v>334.688460516676</v>
+      </c>
+      <c r="O16" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="P16" s="96" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="91" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="100" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="100" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="101" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="101" t="s">
+        <v>201</v>
+      </c>
+      <c r="F20" s="101" t="s">
+        <v>202</v>
+      </c>
+      <c r="G20" s="101" t="s">
+        <v>203</v>
+      </c>
+      <c r="H20" s="102" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="102" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="94"/>
+      <c r="L20" t="s">
+        <v>204</v>
+      </c>
+      <c r="N20" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="104">
+        <v>0</v>
+      </c>
+      <c r="C21" s="104">
+        <v>0</v>
+      </c>
+      <c r="D21" s="104">
+        <v>0</v>
+      </c>
+      <c r="E21" s="104">
+        <v>0</v>
+      </c>
+      <c r="F21" s="104">
+        <f>B22/3.4</f>
+        <v>4083.6764705882356</v>
+      </c>
+      <c r="G21" s="104">
+        <f>C22/3.4</f>
+        <v>9903.9705882352937</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" s="93"/>
+      <c r="L21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
+        <v>13884.5</v>
+      </c>
+      <c r="C22" s="5">
+        <v>33673.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>13884.5</v>
+      </c>
+      <c r="E22" s="5">
+        <v>33673.5</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="105">
+        <v>83</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="105">
+        <v>83</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="105">
+        <v>83</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="92" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="105">
+        <v>695</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0</v>
+      </c>
+      <c r="D24" s="105">
+        <v>695</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="F24" s="105">
+        <v>695</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="91" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="107" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="107" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="108" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="C30" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="D30" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
+    <tabColor theme="2" tint="-9.9978637043366805E-2"/>
   </sheetPr>
   <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -60000,723 +60088,10 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor rgb="FF305496"/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="4" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="100" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="45">
-        <v>71300</v>
-      </c>
-      <c r="C3" s="45">
-        <v>110658</v>
-      </c>
-      <c r="D3" s="45">
-        <v>127302</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="45">
-        <v>0</v>
-      </c>
-      <c r="C4" s="45">
-        <v>12789</v>
-      </c>
-      <c r="D4" s="45">
-        <v>11850</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="9">
-        <v>300</v>
-      </c>
-      <c r="C5" s="9">
-        <v>320</v>
-      </c>
-      <c r="D5" s="9">
-        <v>310</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="45">
-        <v>902171.34</v>
-      </c>
-      <c r="C6" s="45">
-        <v>902171.34</v>
-      </c>
-      <c r="D6" s="45">
-        <v>902171.34</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="9">
-        <v>100</v>
-      </c>
-      <c r="C7" s="9">
-        <v>100</v>
-      </c>
-      <c r="D7" s="9">
-        <v>100</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="10" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="91" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="123" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="124" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="126" t="s">
-        <v>182</v>
-      </c>
-      <c r="E11" s="127" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="127" t="s">
-        <v>184</v>
-      </c>
-      <c r="G11" s="127" t="s">
-        <v>185</v>
-      </c>
-      <c r="H11" s="93" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="124" t="s">
-        <v>187</v>
-      </c>
-      <c r="J11" s="125" t="s">
-        <v>188</v>
-      </c>
-      <c r="K11" s="126" t="s">
-        <v>189</v>
-      </c>
-      <c r="L11" s="93" t="s">
-        <v>190</v>
-      </c>
-      <c r="M11" s="124" t="s">
-        <v>191</v>
-      </c>
-      <c r="N11" s="94" t="s">
-        <v>192</v>
-      </c>
-      <c r="O11" s="123" t="s">
-        <v>62</v>
-      </c>
-      <c r="P11" s="123" t="s">
-        <v>63</v>
-      </c>
-      <c r="R11" s="94"/>
-      <c r="S11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="128" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="129">
-        <v>0</v>
-      </c>
-      <c r="C12" s="130">
-        <v>132.1138129435102</v>
-      </c>
-      <c r="D12" s="29">
-        <v>334.5549512355899</v>
-      </c>
-      <c r="E12" s="79">
-        <v>301.5706207743001</v>
-      </c>
-      <c r="F12" s="79">
-        <v>212.0418932866599</v>
-      </c>
-      <c r="G12" s="79">
-        <v>179.0575628253699</v>
-      </c>
-      <c r="H12" s="131">
-        <v>84.816757314669871</v>
-      </c>
-      <c r="I12" s="129">
-        <v>0</v>
-      </c>
-      <c r="J12" s="130">
-        <v>105.6910503548001</v>
-      </c>
-      <c r="K12" s="29">
-        <v>105.6910503548001</v>
-      </c>
-      <c r="L12" s="131">
-        <f>105.6910503548+0.147</f>
-        <v>105.8380503548</v>
-      </c>
-      <c r="M12" s="129">
-        <v>0</v>
-      </c>
-      <c r="N12" s="132">
-        <v>0</v>
-      </c>
-      <c r="O12" s="129" t="s">
-        <v>194</v>
-      </c>
-      <c r="P12" s="129" t="s">
-        <v>195</v>
-      </c>
-      <c r="R12" s="93"/>
-      <c r="S12" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="133" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="26">
-        <v>440.37930928179981</v>
-      </c>
-      <c r="C13" s="134">
-        <v>317.07315106442002</v>
-      </c>
-      <c r="D13" s="8">
-        <v>317.07315106441979</v>
-      </c>
-      <c r="E13" s="9">
-        <v>317.07315106441979</v>
-      </c>
-      <c r="F13" s="9">
-        <v>317.07315106441979</v>
-      </c>
-      <c r="G13" s="9">
-        <v>317.07315106441979</v>
-      </c>
-      <c r="H13" s="14">
-        <v>317.07315106441979</v>
-      </c>
-      <c r="I13" s="26">
-        <v>484.41738132276009</v>
-      </c>
-      <c r="J13" s="134">
-        <v>264.22762588702</v>
-      </c>
-      <c r="K13" s="8">
-        <v>264.22762588702</v>
-      </c>
-      <c r="L13" s="14">
-        <v>264.22762588702</v>
-      </c>
-      <c r="M13" s="26">
-        <v>493.22483445920028</v>
-      </c>
-      <c r="N13" s="30">
-        <v>0</v>
-      </c>
-      <c r="O13" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="P13" s="26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="133" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="26">
-        <v>598.9160864036869</v>
-      </c>
-      <c r="C14" s="134">
-        <v>607.72374112982209</v>
-      </c>
-      <c r="D14" s="8">
-        <v>654.97377625205797</v>
-      </c>
-      <c r="E14" s="9">
-        <v>631.41349398681803</v>
-      </c>
-      <c r="F14" s="9">
-        <v>654.97377625205797</v>
-      </c>
-      <c r="G14" s="9">
-        <v>560.732862891266</v>
-      </c>
-      <c r="H14" s="14">
-        <v>518.32448423393498</v>
-      </c>
-      <c r="I14" s="26">
-        <v>519.64759704790811</v>
-      </c>
-      <c r="J14" s="134">
-        <v>572.49332381499198</v>
-      </c>
-      <c r="K14" s="135">
-        <v>572.49332381499198</v>
-      </c>
-      <c r="L14" s="136">
-        <v>572.49332381499198</v>
-      </c>
-      <c r="M14" s="26">
-        <v>510.8399423217781</v>
-      </c>
-      <c r="N14" s="30">
-        <v>0</v>
-      </c>
-      <c r="O14" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="P14" s="26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="133" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="26">
-        <v>1277.1002589838199</v>
-      </c>
-      <c r="C15" s="134">
-        <v>158.53657553220989</v>
-      </c>
-      <c r="D15" s="8">
-        <v>306.28280664744801</v>
-      </c>
-      <c r="E15" s="9">
-        <v>282.72252438220801</v>
-      </c>
-      <c r="F15" s="9">
-        <v>193.19379689456511</v>
-      </c>
-      <c r="G15" s="9">
-        <v>169.63351462932499</v>
-      </c>
-      <c r="H15" s="14">
-        <v>80.10478714168201</v>
-      </c>
-      <c r="I15" s="26">
-        <v>317.07315106442002</v>
-      </c>
-      <c r="J15" s="134">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <v>0</v>
-      </c>
-      <c r="M15" s="26">
-        <v>0</v>
-      </c>
-      <c r="N15" s="30">
-        <v>554.87801436273696</v>
-      </c>
-      <c r="O15" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="P15" s="26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="96">
-        <v>0</v>
-      </c>
-      <c r="C16" s="97">
-        <v>563.68566908885987</v>
-      </c>
-      <c r="D16" s="88">
-        <v>339.26702925864407</v>
-      </c>
-      <c r="E16" s="89">
-        <v>400.52372000823402</v>
-      </c>
-      <c r="F16" s="89">
-        <v>513.61251406094698</v>
-      </c>
-      <c r="G16" s="89">
-        <v>527.74885598022911</v>
-      </c>
-      <c r="H16" s="98">
-        <v>654.97388410213307</v>
-      </c>
-      <c r="I16" s="96">
-        <v>0</v>
-      </c>
-      <c r="J16" s="97">
-        <v>704.60713675850002</v>
-      </c>
-      <c r="K16" s="88">
-        <v>735.07856339373586</v>
-      </c>
-      <c r="L16" s="98">
-        <v>673.82208834431788</v>
-      </c>
-      <c r="M16" s="96">
-        <v>0</v>
-      </c>
-      <c r="N16" s="99">
-        <v>334.688460516676</v>
-      </c>
-      <c r="O16" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="P16" s="96" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="91" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B20" s="100" t="s">
-        <v>198</v>
-      </c>
-      <c r="C20" s="100" t="s">
-        <v>199</v>
-      </c>
-      <c r="D20" s="101" t="s">
-        <v>200</v>
-      </c>
-      <c r="E20" s="101" t="s">
-        <v>201</v>
-      </c>
-      <c r="F20" s="101" t="s">
-        <v>202</v>
-      </c>
-      <c r="G20" s="101" t="s">
-        <v>203</v>
-      </c>
-      <c r="H20" s="102" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="K20" s="94"/>
-      <c r="L20" t="s">
-        <v>204</v>
-      </c>
-      <c r="N20" s="33" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="104">
-        <v>0</v>
-      </c>
-      <c r="C21" s="104">
-        <v>0</v>
-      </c>
-      <c r="D21" s="104">
-        <v>0</v>
-      </c>
-      <c r="E21" s="104">
-        <v>0</v>
-      </c>
-      <c r="F21" s="104">
-        <f>B22/3.4</f>
-        <v>4083.6764705882356</v>
-      </c>
-      <c r="G21" s="104">
-        <f>C22/3.4</f>
-        <v>9903.9705882352937</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="K21" s="93"/>
-      <c r="L21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5">
-        <v>13884.5</v>
-      </c>
-      <c r="C22" s="5">
-        <v>33673.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>13884.5</v>
-      </c>
-      <c r="E22" s="5">
-        <v>33673.5</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="105">
-        <v>83</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="105">
-        <v>83</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0</v>
-      </c>
-      <c r="F23" s="105">
-        <v>83</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="105">
-        <v>695</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0</v>
-      </c>
-      <c r="D24" s="105">
-        <v>695</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0</v>
-      </c>
-      <c r="F24" s="105">
-        <v>695</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="92" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="91" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="107" t="s">
-        <v>210</v>
-      </c>
-      <c r="C29" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="100" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="108" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="102" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="92" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="C30" s="9">
-        <v>21.8</v>
-      </c>
-      <c r="D30" s="9">
-        <v>62.5</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -60730,7 +60105,9 @@
     <col min="9" max="9" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -62621,7 +61998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -63221,7 +62598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -64127,4 +63504,631 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF46BECF"/>
+  </sheetPr>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" customWidth="1"/>
+    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="92" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="92" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="92" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1" s="92" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="9">
+        <v>75</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>303.58</v>
+      </c>
+      <c r="D5" s="9">
+        <v>418.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="9">
+        <v>333</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="9">
+        <v>33333</v>
+      </c>
+      <c r="C15" s="9">
+        <v>1097.24</v>
+      </c>
+      <c r="D15" s="9">
+        <v>6006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="92" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="92" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="9">
+        <v>5117</v>
+      </c>
+      <c r="C22" s="9">
+        <v>191.61</v>
+      </c>
+      <c r="D22" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="92" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="92" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0</v>
+      </c>
+      <c r="C35" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="92" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="9">
+        <v>135</v>
+      </c>
+      <c r="C37" s="9">
+        <v>21.76</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="92" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="92" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="9">
+        <v>0</v>
+      </c>
+      <c r="C41" s="9">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="238" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0</v>
+      </c>
+      <c r="C42" s="9">
+        <v>2.15</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB13344-461F-0349-86DF-F6BB1EC7E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CDFDD5-762F-8941-9158-1C845201A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="37600" windowHeight="19620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="37600" windowHeight="19620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Battery_Capacity!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Mapping!$A$1:$H$691</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">MI!$A$1:$G$829</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">MI!$A$1:$G$837</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">MI_Energy!$A$1:$AG$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">MS_Energy_Ag!$A$1:$S$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MS_Energy_Disag!$A$1:$AF$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MS_Energy_Disag!$A$1:$AF$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Overrides!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -5759,15 +5759,33 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5777,21 +5795,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5812,36 +5819,31 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5854,16 +5856,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -6343,18 +6343,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="252" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="257"/>
+      <c r="B1" s="253"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="258"/>
-      <c r="B2" s="259"/>
+      <c r="A2" s="254"/>
+      <c r="B2" s="255"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="260"/>
-      <c r="B3" s="261"/>
+      <c r="A3" s="256"/>
+      <c r="B3" s="257"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
@@ -6363,10 +6363,10 @@
       <c r="B4" s="122"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="263" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="250"/>
+      <c r="B5" s="248"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="35" t="s">
@@ -6377,10 +6377,10 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="249" t="s">
+      <c r="A7" s="260" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="250"/>
+      <c r="B7" s="248"/>
     </row>
     <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="116" t="s">
@@ -6407,13 +6407,13 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="252" t="s">
+      <c r="A11" s="262" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="250"/>
+      <c r="B11" s="248"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="246" t="s">
+      <c r="A12" s="259" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -6421,13 +6421,13 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="247"/>
+      <c r="A13" s="250"/>
       <c r="B13" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="248"/>
+      <c r="A14" s="251"/>
       <c r="B14" s="9" t="s">
         <v>83</v>
       </c>
@@ -6465,10 +6465,10 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="251" t="s">
+      <c r="A19" s="261" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="250"/>
+      <c r="B19" s="248"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="110" t="s">
@@ -6479,7 +6479,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="262" t="s">
+      <c r="A21" s="258" t="s">
         <v>95</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -6487,19 +6487,19 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="248"/>
+      <c r="A22" s="251"/>
       <c r="B22" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="255" t="s">
+      <c r="A23" s="249" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="250"/>
+      <c r="B23" s="248"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="255" t="s">
+      <c r="A24" s="249" t="s">
         <v>99</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -6507,19 +6507,19 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="247"/>
+      <c r="A25" s="250"/>
       <c r="B25" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="247"/>
+      <c r="A26" s="250"/>
       <c r="B26" s="9" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="248"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="9" t="s">
         <v>103</v>
       </c>
@@ -6557,10 +6557,10 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="254" t="s">
+      <c r="A32" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="250"/>
+      <c r="B32" s="248"/>
     </row>
     <row r="33" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="77" t="s">
@@ -17782,7 +17782,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G837"/>
@@ -17819,7 +17819,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="79" t="s">
         <v>137</v>
       </c>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>137</v>
       </c>
@@ -17861,7 +17861,7 @@
       </c>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>137</v>
       </c>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>137</v>
       </c>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>1046</v>
       </c>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>1046</v>
       </c>
@@ -17946,7 +17946,7 @@
       </c>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>1046</v>
       </c>
@@ -17969,7 +17969,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>1046</v>
       </c>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>1046</v>
       </c>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>138</v>
       </c>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>138</v>
       </c>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>138</v>
       </c>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>1055</v>
       </c>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>1055</v>
       </c>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>1056</v>
       </c>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>1056</v>
       </c>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>1056</v>
       </c>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>1061</v>
       </c>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>1061</v>
       </c>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>1061</v>
       </c>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>1061</v>
       </c>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18285,7 +18285,7 @@
       </c>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18349,7 +18349,7 @@
       </c>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18414,7 +18414,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18437,7 +18437,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18460,7 +18460,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18483,7 +18483,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>1066</v>
       </c>
@@ -18506,7 +18506,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18529,7 +18529,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18575,7 +18575,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18621,7 +18621,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>1078</v>
       </c>
@@ -18667,7 +18667,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>1093</v>
       </c>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>1093</v>
       </c>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>1093</v>
       </c>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>1095</v>
       </c>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>1095</v>
       </c>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18795,7 +18795,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18904,7 +18904,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="G53" s="9"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18971,7 +18971,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
         <v>1096</v>
       </c>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="G55" s="9"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="G56" s="9"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="G57" s="9"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19078,7 +19078,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19147,7 +19147,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="G63" s="9"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="G66" s="9"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="G67" s="9"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
         <v>1056</v>
       </c>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="G68" s="9"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="G69" s="9"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="G71" s="9"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19365,7 +19365,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19386,7 +19386,7 @@
       </c>
       <c r="G73" s="9"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9" t="s">
         <v>137</v>
       </c>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="G74" s="9"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9" t="s">
         <v>137</v>
       </c>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="G75" s="9"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
         <v>1046</v>
       </c>
@@ -19449,7 +19449,7 @@
       </c>
       <c r="G76" s="9"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9" t="s">
         <v>1046</v>
       </c>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="G77" s="9"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9" t="s">
         <v>1046</v>
       </c>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="G78" s="9"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
         <v>1046</v>
       </c>
@@ -19512,7 +19512,7 @@
       </c>
       <c r="G79" s="9"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
         <v>138</v>
       </c>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="G80" s="9"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
         <v>138</v>
       </c>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="G81" s="9"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9" t="s">
         <v>1055</v>
       </c>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="G82" s="9"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9" t="s">
         <v>1055</v>
       </c>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="G83" s="9"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9" t="s">
         <v>1056</v>
       </c>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="G84" s="9"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9" t="s">
         <v>1056</v>
       </c>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="G85" s="9"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9" t="s">
         <v>1056</v>
       </c>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="G86" s="9"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9" t="s">
         <v>1061</v>
       </c>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="G87" s="9"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9" t="s">
         <v>1061</v>
       </c>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="G88" s="9"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9" t="s">
         <v>1061</v>
       </c>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="G89" s="9"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9" t="s">
         <v>1061</v>
       </c>
@@ -19743,7 +19743,7 @@
       </c>
       <c r="G90" s="9"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19766,7 +19766,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9" t="s">
         <v>1066</v>
       </c>
@@ -19789,7 +19789,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9" t="s">
         <v>1093</v>
       </c>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="G93" s="9"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9" t="s">
         <v>1093</v>
       </c>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="G94" s="9"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9" t="s">
         <v>1093</v>
       </c>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="G95" s="9"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19875,7 +19875,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19898,7 +19898,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="G98" s="9"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19965,7 +19965,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9" t="s">
         <v>1096</v>
       </c>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="G101" s="9"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9" t="s">
         <v>1096</v>
       </c>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G102" s="9"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9" t="s">
         <v>1096</v>
       </c>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="G103" s="9"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9" t="s">
         <v>1096</v>
       </c>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="G104" s="9"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9" t="s">
         <v>1056</v>
       </c>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="G105" s="9"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9" t="s">
         <v>144</v>
       </c>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="G106" s="9"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9" t="s">
         <v>137</v>
       </c>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="G107" s="9"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9" t="s">
         <v>137</v>
       </c>
@@ -20133,7 +20133,7 @@
       </c>
       <c r="G108" s="9"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9" t="s">
         <v>1046</v>
       </c>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G109" s="9"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9" t="s">
         <v>1046</v>
       </c>
@@ -20175,7 +20175,7 @@
       </c>
       <c r="G110" s="9"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9" t="s">
         <v>1061</v>
       </c>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="G111" s="9"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20219,7 +20219,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G114" s="9"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="G116" s="9"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20330,7 +20330,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20351,7 +20351,7 @@
       </c>
       <c r="G118" s="9"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20420,7 +20420,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20441,7 +20441,7 @@
       </c>
       <c r="G122" s="9"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="G123" s="9"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20486,7 +20486,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="79" t="s">
         <v>1078</v>
       </c>
@@ -20509,7 +20509,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20530,7 +20530,7 @@
       </c>
       <c r="G126" s="9"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20576,7 +20576,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20599,7 +20599,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20620,7 +20620,7 @@
       </c>
       <c r="G130" s="9"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20643,7 +20643,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20666,7 +20666,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="G133" s="9"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="G135" s="9"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20777,7 +20777,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20823,7 +20823,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9" t="s">
         <v>1078</v>
       </c>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="G140" s="9"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9" t="s">
         <v>137</v>
       </c>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="G141" s="9"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9" t="s">
         <v>138</v>
       </c>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="G142" s="9"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9" t="s">
         <v>1061</v>
       </c>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="G143" s="9"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9" t="s">
         <v>1066</v>
       </c>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="G144" s="9"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9" t="s">
         <v>1066</v>
       </c>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="G145" s="9"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9" t="s">
         <v>1066</v>
       </c>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="G146" s="9"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9" t="s">
         <v>1066</v>
       </c>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="G147" s="9"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9" t="s">
         <v>1066</v>
       </c>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="G148" s="9"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21035,7 +21035,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21079,7 +21079,7 @@
       </c>
       <c r="G151" s="9"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21100,7 +21100,7 @@
       </c>
       <c r="G152" s="9"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21146,7 +21146,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="G155" s="9"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9" t="s">
         <v>1096</v>
       </c>
@@ -21188,7 +21188,7 @@
       </c>
       <c r="G156" s="9"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9" t="s">
         <v>137</v>
       </c>
@@ -21209,7 +21209,7 @@
       </c>
       <c r="G157" s="9"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9" t="s">
         <v>137</v>
       </c>
@@ -21231,7 +21231,7 @@
       </c>
       <c r="G158" s="9"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="9" t="s">
         <v>137</v>
       </c>
@@ -21253,7 +21253,7 @@
       </c>
       <c r="G159" s="9"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9" t="s">
         <v>137</v>
       </c>
@@ -21274,7 +21274,7 @@
       </c>
       <c r="G160" s="9"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21295,7 +21295,7 @@
       </c>
       <c r="G161" s="9"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21316,7 +21316,7 @@
       </c>
       <c r="G162" s="9"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="G163" s="9"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="G164" s="9"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G165" s="9"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="G166" s="9"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="G167" s="9"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21442,7 +21442,7 @@
       </c>
       <c r="G168" s="9"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21486,7 +21486,7 @@
       </c>
       <c r="G170" s="9"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="9" t="s">
         <v>1046</v>
       </c>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="G171" s="9"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="9" t="s">
         <v>138</v>
       </c>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G172" s="9"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="9" t="s">
         <v>138</v>
       </c>
@@ -21549,7 +21549,7 @@
       </c>
       <c r="G173" s="9"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="9" t="s">
         <v>138</v>
       </c>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="G174" s="9"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9" t="s">
         <v>138</v>
       </c>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="G175" s="9"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="9" t="s">
         <v>138</v>
       </c>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="G176" s="9"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="9" t="s">
         <v>1055</v>
       </c>
@@ -21633,7 +21633,7 @@
       </c>
       <c r="G177" s="9"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="9" t="s">
         <v>1055</v>
       </c>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="G178" s="9"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="9" t="s">
         <v>1055</v>
       </c>
@@ -21675,7 +21675,7 @@
       </c>
       <c r="G179" s="9"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="9" t="s">
         <v>1055</v>
       </c>
@@ -21696,7 +21696,7 @@
       </c>
       <c r="G180" s="9"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="G181" s="9"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="G182" s="9"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="G183" s="9"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21780,7 +21780,7 @@
       </c>
       <c r="G184" s="9"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="G185" s="9"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21822,7 +21822,7 @@
       </c>
       <c r="G186" s="9"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="G187" s="9"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="9" t="s">
         <v>1056</v>
       </c>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="G188" s="9"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21885,7 +21885,7 @@
       </c>
       <c r="G189" s="9"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="G190" s="9"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="G191" s="9"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21948,7 +21948,7 @@
       </c>
       <c r="G192" s="9"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21969,7 +21969,7 @@
       </c>
       <c r="G193" s="9"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="9" t="s">
         <v>1061</v>
       </c>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="G194" s="9"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="9" t="s">
         <v>1061</v>
       </c>
@@ -22011,7 +22011,7 @@
       </c>
       <c r="G195" s="9"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="G196" s="9"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22053,7 +22053,7 @@
       </c>
       <c r="G197" s="9"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="G198" s="9"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22096,7 +22096,7 @@
       </c>
       <c r="G199" s="9"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="G200" s="9"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22140,7 +22140,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22161,7 +22161,7 @@
       </c>
       <c r="G202" s="9"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22182,7 +22182,7 @@
       </c>
       <c r="G203" s="9"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22205,7 +22205,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="G205" s="9"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="G206" s="9"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22270,7 +22270,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="G208" s="9"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="9" t="s">
         <v>1066</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22337,7 +22337,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22406,7 +22406,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22427,7 +22427,7 @@
       </c>
       <c r="G214" s="9"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22450,7 +22450,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22496,7 +22496,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22519,7 +22519,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22565,7 +22565,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22588,7 +22588,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22611,7 +22611,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22634,7 +22634,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22657,7 +22657,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22703,7 +22703,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22749,7 +22749,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="9" t="s">
         <v>1078</v>
       </c>
@@ -22772,7 +22772,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="9" t="s">
         <v>1095</v>
       </c>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="G230" s="9"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="9" t="s">
         <v>1095</v>
       </c>
@@ -22816,7 +22816,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9" t="s">
         <v>1095</v>
       </c>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="G232" s="9"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="9" t="s">
         <v>1095</v>
       </c>
@@ -22860,7 +22860,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="G234" s="9"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22927,7 +22927,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22948,7 +22948,7 @@
       </c>
       <c r="G237" s="9"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22971,7 +22971,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="9" t="s">
         <v>1096</v>
       </c>
@@ -22994,7 +22994,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="G240" s="9"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="G241" s="9"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="G242" s="9"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="G243" s="9"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23099,7 +23099,7 @@
       </c>
       <c r="G244" s="9"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23120,7 +23120,7 @@
       </c>
       <c r="G245" s="9"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="G246" s="9"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="G247" s="9"/>
     </row>
-    <row r="248" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23206,7 +23206,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="9" t="s">
         <v>144</v>
       </c>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="G250" s="9"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="9" t="s">
         <v>1056</v>
       </c>
@@ -23249,7 +23249,7 @@
       </c>
       <c r="G251" s="9"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23293,7 +23293,7 @@
       </c>
       <c r="G253" s="9"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23339,7 +23339,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="9" t="s">
         <v>1095</v>
       </c>
@@ -23360,7 +23360,7 @@
       </c>
       <c r="G256" s="9"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23381,7 +23381,7 @@
       </c>
       <c r="G257" s="9"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23404,7 +23404,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23450,7 +23450,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23473,7 +23473,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="G262" s="9"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23515,7 +23515,7 @@
       </c>
       <c r="G263" s="9"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="G264" s="9"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="9" t="s">
         <v>1061</v>
       </c>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="G265" s="9"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23578,7 +23578,7 @@
       </c>
       <c r="G266" s="9"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23601,7 +23601,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23622,7 +23622,7 @@
       </c>
       <c r="G268" s="9"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23643,7 +23643,7 @@
       </c>
       <c r="G269" s="9"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23666,7 +23666,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="G271" s="9"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23708,7 +23708,7 @@
       </c>
       <c r="G272" s="9"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="G273" s="9"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="9" t="s">
         <v>1061</v>
       </c>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="G274" s="9"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G275" s="9"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="G276" s="9"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="G277" s="9"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="G278" s="9"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23855,7 +23855,7 @@
       </c>
       <c r="G279" s="9"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="9" t="s">
         <v>1066</v>
       </c>
@@ -23876,7 +23876,7 @@
       </c>
       <c r="G280" s="9"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23899,7 +23899,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23922,7 +23922,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23943,7 +23943,7 @@
       </c>
       <c r="G283" s="9"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23964,7 +23964,7 @@
       </c>
       <c r="G284" s="9"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="9" t="s">
         <v>1096</v>
       </c>
@@ -23987,7 +23987,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="9" t="s">
         <v>1096</v>
       </c>
@@ -24010,7 +24010,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="9" t="s">
         <v>1096</v>
       </c>
@@ -24031,7 +24031,7 @@
       </c>
       <c r="G287" s="9"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="9" t="s">
         <v>1096</v>
       </c>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="G288" s="9"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24121,7 +24121,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24144,7 +24144,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24167,7 +24167,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24190,7 +24190,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="9" t="s">
         <v>1078</v>
       </c>
@@ -24213,7 +24213,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="G296" s="9"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24255,7 +24255,7 @@
       </c>
       <c r="G297" s="9"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="G298" s="9"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="G299" s="9"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="G300" s="9"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="G301" s="9"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="G302" s="9"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24383,7 +24383,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24404,7 +24404,7 @@
       </c>
       <c r="G304" s="9"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="G305" s="9"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="9" t="s">
         <v>1066</v>
       </c>
@@ -24448,7 +24448,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24469,7 +24469,7 @@
       </c>
       <c r="G307" s="9"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="9" t="s">
         <v>137</v>
       </c>
@@ -24490,7 +24490,7 @@
       </c>
       <c r="G308" s="9"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="9" t="s">
         <v>137</v>
       </c>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="G309" s="9"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="9" t="s">
         <v>137</v>
       </c>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="G310" s="9"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="9" t="s">
         <v>137</v>
       </c>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="G311" s="9"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="9" t="s">
         <v>1046</v>
       </c>
@@ -24577,7 +24577,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="79" t="s">
         <v>1046</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="9" t="s">
         <v>1046</v>
       </c>
@@ -24623,7 +24623,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="9" t="s">
         <v>1046</v>
       </c>
@@ -24644,7 +24644,7 @@
       </c>
       <c r="G315" s="9"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="9" t="s">
         <v>1046</v>
       </c>
@@ -24665,7 +24665,7 @@
       </c>
       <c r="G316" s="9"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="9" t="s">
         <v>138</v>
       </c>
@@ -24686,7 +24686,7 @@
       </c>
       <c r="G317" s="9"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="9" t="s">
         <v>138</v>
       </c>
@@ -24709,7 +24709,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="9" t="s">
         <v>138</v>
       </c>
@@ -24730,7 +24730,7 @@
       </c>
       <c r="G319" s="9"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="9" t="s">
         <v>138</v>
       </c>
@@ -24753,7 +24753,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="9" t="s">
         <v>138</v>
       </c>
@@ -24774,7 +24774,7 @@
       </c>
       <c r="G321" s="9"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="79" t="s">
         <v>138</v>
       </c>
@@ -24797,7 +24797,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="9" t="s">
         <v>138</v>
       </c>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="G323" s="9"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="9" t="s">
         <v>138</v>
       </c>
@@ -24841,7 +24841,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="9" t="s">
         <v>138</v>
       </c>
@@ -24862,7 +24862,7 @@
       </c>
       <c r="G325" s="9"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="9" t="s">
         <v>1055</v>
       </c>
@@ -24883,7 +24883,7 @@
       </c>
       <c r="G326" s="9"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="9" t="s">
         <v>1055</v>
       </c>
@@ -24904,7 +24904,7 @@
       </c>
       <c r="G327" s="9"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="G328" s="9"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24946,7 +24946,7 @@
       </c>
       <c r="G329" s="9"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24967,7 +24967,7 @@
       </c>
       <c r="G330" s="9"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="9" t="s">
         <v>1056</v>
       </c>
@@ -24988,7 +24988,7 @@
       </c>
       <c r="G331" s="9"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="9" t="s">
         <v>1061</v>
       </c>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="G332" s="9"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="9" t="s">
         <v>1061</v>
       </c>
@@ -25030,7 +25030,7 @@
       </c>
       <c r="G333" s="9"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="9" t="s">
         <v>1061</v>
       </c>
@@ -25051,7 +25051,7 @@
       </c>
       <c r="G334" s="9"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="9" t="s">
         <v>1061</v>
       </c>
@@ -25074,7 +25074,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="9" t="s">
         <v>1061</v>
       </c>
@@ -25097,7 +25097,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25120,7 +25120,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25143,7 +25143,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25166,7 +25166,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25189,7 +25189,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25212,7 +25212,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25235,7 +25235,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="G343" s="9"/>
     </row>
-    <row r="344" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25279,7 +25279,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="9" t="s">
         <v>1066</v>
       </c>
@@ -25302,7 +25302,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="9" t="s">
         <v>1093</v>
       </c>
@@ -25323,7 +25323,7 @@
       </c>
       <c r="G346" s="9"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="9" t="s">
         <v>1093</v>
       </c>
@@ -25344,7 +25344,7 @@
       </c>
       <c r="G347" s="9"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="9" t="s">
         <v>1093</v>
       </c>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="G348" s="9"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25386,7 +25386,7 @@
       </c>
       <c r="G349" s="9"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25409,7 +25409,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25432,7 +25432,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25455,7 +25455,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25478,7 +25478,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="G354" s="9"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25520,7 +25520,7 @@
       </c>
       <c r="G355" s="9"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25543,7 +25543,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25566,7 +25566,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25589,7 +25589,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25612,7 +25612,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25635,7 +25635,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25658,7 +25658,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25681,7 +25681,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25704,7 +25704,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25727,7 +25727,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="9" t="s">
         <v>1096</v>
       </c>
@@ -25748,7 +25748,7 @@
       </c>
       <c r="G365" s="9"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="9" t="s">
         <v>144</v>
       </c>
@@ -25769,7 +25769,7 @@
       </c>
       <c r="G366" s="9"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="9" t="s">
         <v>137</v>
       </c>
@@ -25790,7 +25790,7 @@
       </c>
       <c r="G367" s="9"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="9" t="s">
         <v>137</v>
       </c>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="G368" s="9"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="9" t="s">
         <v>1046</v>
       </c>
@@ -25832,7 +25832,7 @@
       </c>
       <c r="G369" s="9"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="9" t="s">
         <v>1046</v>
       </c>
@@ -25853,7 +25853,7 @@
       </c>
       <c r="G370" s="9"/>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="9" t="s">
         <v>138</v>
       </c>
@@ -25874,7 +25874,7 @@
       </c>
       <c r="G371" s="9"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="9" t="s">
         <v>1055</v>
       </c>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="G372" s="9"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="9" t="s">
         <v>1055</v>
       </c>
@@ -25916,7 +25916,7 @@
       </c>
       <c r="G373" s="9"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="9" t="s">
         <v>1056</v>
       </c>
@@ -25937,7 +25937,7 @@
       </c>
       <c r="G374" s="9"/>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="9" t="s">
         <v>1056</v>
       </c>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="G375" s="9"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="9" t="s">
         <v>1056</v>
       </c>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="G376" s="9"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="9" t="s">
         <v>1056</v>
       </c>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="G377" s="9"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26021,7 +26021,7 @@
       </c>
       <c r="G378" s="9"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26044,7 +26044,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26065,7 +26065,7 @@
       </c>
       <c r="G380" s="9"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26086,7 +26086,7 @@
       </c>
       <c r="G381" s="9"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26109,7 +26109,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26130,7 +26130,7 @@
       </c>
       <c r="G383" s="9"/>
     </row>
-    <row r="384" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="9" t="s">
         <v>1066</v>
       </c>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="G384" s="9"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="9" t="s">
         <v>1093</v>
       </c>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="G385" s="9"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="9" t="s">
         <v>1093</v>
       </c>
@@ -26193,7 +26193,7 @@
       </c>
       <c r="G386" s="9"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="9" t="s">
         <v>1093</v>
       </c>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="G387" s="9"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="9" t="s">
         <v>1096</v>
       </c>
@@ -26235,7 +26235,7 @@
       </c>
       <c r="G388" s="9"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26258,7 +26258,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26281,7 +26281,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26302,7 +26302,7 @@
       </c>
       <c r="G391" s="9"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26323,7 +26323,7 @@
       </c>
       <c r="G392" s="9"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26346,7 +26346,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="G394" s="9"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26390,7 +26390,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26411,7 +26411,7 @@
       </c>
       <c r="G396" s="9"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26434,7 +26434,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26457,7 +26457,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26480,7 +26480,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26501,7 +26501,7 @@
       </c>
       <c r="G400" s="9"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26522,7 +26522,7 @@
       </c>
       <c r="G401" s="9"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26545,7 +26545,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26568,7 +26568,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="G404" s="9"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26612,7 +26612,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26635,7 +26635,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26658,7 +26658,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26679,7 +26679,7 @@
       </c>
       <c r="G408" s="9"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26702,7 +26702,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26725,7 +26725,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26746,7 +26746,7 @@
       </c>
       <c r="G411" s="9"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26769,7 +26769,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="G413" s="9"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26813,7 +26813,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26836,7 +26836,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26859,7 +26859,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26882,7 +26882,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="9" t="s">
         <v>1078</v>
       </c>
@@ -26903,7 +26903,7 @@
       </c>
       <c r="G418" s="9"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="9" t="s">
         <v>1046</v>
       </c>
@@ -26924,7 +26924,7 @@
       </c>
       <c r="G419" s="9"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="9" t="s">
         <v>138</v>
       </c>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="G420" s="9"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="9" t="s">
         <v>1055</v>
       </c>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="G421" s="9"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="9" t="s">
         <v>1055</v>
       </c>
@@ -26987,7 +26987,7 @@
       </c>
       <c r="G422" s="9"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="9" t="s">
         <v>1056</v>
       </c>
@@ -27008,7 +27008,7 @@
       </c>
       <c r="G423" s="9"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="9" t="s">
         <v>1056</v>
       </c>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="G424" s="9"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="G425" s="9"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27071,7 +27071,7 @@
       </c>
       <c r="G426" s="9"/>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27092,7 +27092,7 @@
       </c>
       <c r="G427" s="9"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27113,7 +27113,7 @@
       </c>
       <c r="G428" s="9"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27134,7 +27134,7 @@
       </c>
       <c r="G429" s="9"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="9" t="s">
         <v>137</v>
       </c>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="G430" s="9"/>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="9" t="s">
         <v>1046</v>
       </c>
@@ -27176,7 +27176,7 @@
       </c>
       <c r="G431" s="9"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="9" t="s">
         <v>1046</v>
       </c>
@@ -27197,7 +27197,7 @@
       </c>
       <c r="G432" s="9"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="9" t="s">
         <v>1046</v>
       </c>
@@ -27218,7 +27218,7 @@
       </c>
       <c r="G433" s="9"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="9" t="s">
         <v>138</v>
       </c>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="G434" s="9"/>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="9" t="s">
         <v>138</v>
       </c>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="G435" s="9"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="9" t="s">
         <v>1055</v>
       </c>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="G436" s="9"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="9" t="s">
         <v>1055</v>
       </c>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="G437" s="9"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="9" t="s">
         <v>1056</v>
       </c>
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G438" s="9"/>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="9" t="s">
         <v>1056</v>
       </c>
@@ -27344,7 +27344,7 @@
       </c>
       <c r="G439" s="9"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="9" t="s">
         <v>1056</v>
       </c>
@@ -27365,7 +27365,7 @@
       </c>
       <c r="G440" s="9"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27386,7 +27386,7 @@
       </c>
       <c r="G441" s="9"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27407,7 +27407,7 @@
       </c>
       <c r="G442" s="9"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27428,7 +27428,7 @@
       </c>
       <c r="G443" s="9"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="G444" s="9"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="9" t="s">
         <v>1061</v>
       </c>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="G445" s="9"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27516,7 +27516,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27539,7 +27539,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27562,7 +27562,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27583,7 +27583,7 @@
       </c>
       <c r="G450" s="9"/>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27606,7 +27606,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27629,7 +27629,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27652,7 +27652,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27673,7 +27673,7 @@
       </c>
       <c r="G454" s="9"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27696,7 +27696,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27719,7 +27719,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27765,7 +27765,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27788,7 +27788,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="G460" s="9"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27832,7 +27832,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27855,7 +27855,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="G463" s="9"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27899,7 +27899,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27920,7 +27920,7 @@
       </c>
       <c r="G465" s="9"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27943,7 +27943,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27966,7 +27966,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="9" t="s">
         <v>1078</v>
       </c>
@@ -27989,7 +27989,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="9" t="s">
         <v>1078</v>
       </c>
@@ -28012,7 +28012,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="9" t="s">
         <v>1078</v>
       </c>
@@ -28033,7 +28033,7 @@
       </c>
       <c r="G470" s="9"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28056,7 +28056,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28102,7 +28102,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28125,7 +28125,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="G475" s="9"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28167,7 +28167,7 @@
       </c>
       <c r="G476" s="9"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="G477" s="9"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28209,7 +28209,7 @@
       </c>
       <c r="G478" s="9"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="9" t="s">
         <v>138</v>
       </c>
@@ -28230,7 +28230,7 @@
       </c>
       <c r="G479" s="9"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="9" t="s">
         <v>1055</v>
       </c>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="G480" s="9"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="9" t="s">
         <v>1055</v>
       </c>
@@ -28272,7 +28272,7 @@
       </c>
       <c r="G481" s="9"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28293,7 +28293,7 @@
       </c>
       <c r="G482" s="9"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="G483" s="9"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G484" s="9"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="G485" s="9"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="G486" s="9"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="9" t="s">
         <v>1056</v>
       </c>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="G487" s="9"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="9" t="s">
         <v>1061</v>
       </c>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="G488" s="9"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="9" t="s">
         <v>1061</v>
       </c>
@@ -28440,7 +28440,7 @@
       </c>
       <c r="G489" s="9"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="9" t="s">
         <v>1061</v>
       </c>
@@ -28461,7 +28461,7 @@
       </c>
       <c r="G490" s="9"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="9" t="s">
         <v>1061</v>
       </c>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="G491" s="9"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="9" t="s">
         <v>1061</v>
       </c>
@@ -28503,7 +28503,7 @@
       </c>
       <c r="G492" s="9"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="9" t="s">
         <v>1066</v>
       </c>
@@ -28526,7 +28526,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="9" t="s">
         <v>1066</v>
       </c>
@@ -28549,7 +28549,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="9" t="s">
         <v>1066</v>
       </c>
@@ -28572,7 +28572,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28595,7 +28595,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28618,7 +28618,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28641,7 +28641,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28664,7 +28664,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28685,7 +28685,7 @@
       </c>
       <c r="G500" s="9"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="G501" s="9"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="G502" s="9"/>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28748,7 +28748,7 @@
       </c>
       <c r="G503" s="9"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="9" t="s">
         <v>144</v>
       </c>
@@ -28769,7 +28769,7 @@
       </c>
       <c r="G504" s="9"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="9" t="s">
         <v>1095</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="9" t="s">
         <v>1095</v>
       </c>
@@ -28813,7 +28813,7 @@
       </c>
       <c r="G506" s="9"/>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="9" t="s">
         <v>1095</v>
       </c>
@@ -28836,7 +28836,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="9" t="s">
         <v>1095</v>
       </c>
@@ -28859,7 +28859,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="9" t="s">
         <v>1095</v>
       </c>
@@ -28880,7 +28880,7 @@
       </c>
       <c r="G509" s="9"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28901,7 +28901,7 @@
       </c>
       <c r="G510" s="9"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28924,7 +28924,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28947,7 +28947,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28968,7 +28968,7 @@
       </c>
       <c r="G513" s="9"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="9" t="s">
         <v>1096</v>
       </c>
@@ -28991,7 +28991,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="9" t="s">
         <v>1096</v>
       </c>
@@ -29014,7 +29014,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="9" t="s">
         <v>1096</v>
       </c>
@@ -29035,7 +29035,7 @@
       </c>
       <c r="G516" s="9"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="9" t="s">
         <v>1096</v>
       </c>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="G517" s="9"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="9" t="s">
         <v>1096</v>
       </c>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="G518" s="9"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="9" t="s">
         <v>137</v>
       </c>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="G519" s="9"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="9" t="s">
         <v>137</v>
       </c>
@@ -29119,7 +29119,7 @@
       </c>
       <c r="G520" s="9"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="9" t="s">
         <v>1046</v>
       </c>
@@ -29140,7 +29140,7 @@
       </c>
       <c r="G521" s="9"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="9" t="s">
         <v>1046</v>
       </c>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="G522" s="9"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="9" t="s">
         <v>1046</v>
       </c>
@@ -29182,7 +29182,7 @@
       </c>
       <c r="G523" s="9"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="9" t="s">
         <v>1046</v>
       </c>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="G524" s="9"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="9" t="s">
         <v>138</v>
       </c>
@@ -29224,7 +29224,7 @@
       </c>
       <c r="G525" s="9"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="9" t="s">
         <v>138</v>
       </c>
@@ -29245,7 +29245,7 @@
       </c>
       <c r="G526" s="9"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="9" t="s">
         <v>1055</v>
       </c>
@@ -29266,7 +29266,7 @@
       </c>
       <c r="G527" s="9"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29287,7 +29287,7 @@
       </c>
       <c r="G528" s="9"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29308,7 +29308,7 @@
       </c>
       <c r="G529" s="9"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29329,7 +29329,7 @@
       </c>
       <c r="G530" s="9"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29350,7 +29350,7 @@
       </c>
       <c r="G531" s="9"/>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="G532" s="9"/>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29392,7 +29392,7 @@
       </c>
       <c r="G533" s="9"/>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29413,7 +29413,7 @@
       </c>
       <c r="G534" s="9"/>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="9" t="s">
         <v>1056</v>
       </c>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="G535" s="9"/>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29455,7 +29455,7 @@
       </c>
       <c r="G536" s="9"/>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29476,7 +29476,7 @@
       </c>
       <c r="G537" s="9"/>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29497,7 +29497,7 @@
       </c>
       <c r="G538" s="9"/>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29518,7 +29518,7 @@
       </c>
       <c r="G539" s="9"/>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29539,7 +29539,7 @@
       </c>
       <c r="G540" s="9"/>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="G541" s="9"/>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="9" t="s">
         <v>1061</v>
       </c>
@@ -29581,7 +29581,7 @@
       </c>
       <c r="G542" s="9"/>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29602,7 +29602,7 @@
       </c>
       <c r="G543" s="9"/>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29625,7 +29625,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="G545" s="9"/>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29669,7 +29669,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29690,7 +29690,7 @@
       </c>
       <c r="G547" s="9"/>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="9" t="s">
         <v>1066</v>
       </c>
@@ -29713,7 +29713,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29736,7 +29736,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29759,7 +29759,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29782,7 +29782,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29805,7 +29805,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29826,7 +29826,7 @@
       </c>
       <c r="G553" s="9"/>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29849,7 +29849,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29872,7 +29872,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29895,7 +29895,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="G557" s="9"/>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29939,7 +29939,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="9" t="s">
         <v>1078</v>
       </c>
@@ -29985,7 +29985,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30008,7 +30008,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30031,7 +30031,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="G563" s="9"/>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30075,7 +30075,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30098,7 +30098,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="G566" s="9"/>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30142,7 +30142,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="G568" s="9"/>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30186,7 +30186,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30209,7 +30209,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30232,7 +30232,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30255,7 +30255,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="9" t="s">
         <v>1078</v>
       </c>
@@ -30276,7 +30276,7 @@
       </c>
       <c r="G573" s="9"/>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30299,7 +30299,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30322,7 +30322,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30343,7 +30343,7 @@
       </c>
       <c r="G576" s="9"/>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30366,7 +30366,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30389,7 +30389,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30410,7 +30410,7 @@
       </c>
       <c r="G579" s="9"/>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30431,7 +30431,7 @@
       </c>
       <c r="G580" s="9"/>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30452,7 +30452,7 @@
       </c>
       <c r="G581" s="9"/>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30473,7 +30473,7 @@
       </c>
       <c r="G582" s="9"/>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30494,7 +30494,7 @@
       </c>
       <c r="G583" s="9"/>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30538,7 +30538,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="9" t="s">
         <v>144</v>
       </c>
@@ -30559,7 +30559,7 @@
       </c>
       <c r="G586" s="9"/>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="9" t="s">
         <v>138</v>
       </c>
@@ -30580,7 +30580,7 @@
       </c>
       <c r="G587" s="9"/>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="9" t="s">
         <v>1056</v>
       </c>
@@ -30601,7 +30601,7 @@
       </c>
       <c r="G588" s="9"/>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="9" t="s">
         <v>1056</v>
       </c>
@@ -30622,7 +30622,7 @@
       </c>
       <c r="G589" s="9"/>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="9" t="s">
         <v>1056</v>
       </c>
@@ -30643,7 +30643,7 @@
       </c>
       <c r="G590" s="9"/>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="9" t="s">
         <v>1061</v>
       </c>
@@ -30664,7 +30664,7 @@
       </c>
       <c r="G591" s="9"/>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="9" t="s">
         <v>1061</v>
       </c>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="G592" s="9"/>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="9" t="s">
         <v>1061</v>
       </c>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="G593" s="9"/>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="9" t="s">
         <v>138</v>
       </c>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="G594" s="9"/>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="9" t="s">
         <v>1061</v>
       </c>
@@ -30748,7 +30748,7 @@
       </c>
       <c r="G595" s="9"/>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30769,7 +30769,7 @@
       </c>
       <c r="G596" s="9"/>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="G597" s="9"/>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="G598" s="9"/>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30832,7 +30832,7 @@
       </c>
       <c r="G599" s="9"/>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30853,7 +30853,7 @@
       </c>
       <c r="G600" s="9"/>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="9" t="s">
         <v>1066</v>
       </c>
@@ -30874,7 +30874,7 @@
       </c>
       <c r="G601" s="9"/>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30897,7 +30897,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30920,7 +30920,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30941,7 +30941,7 @@
       </c>
       <c r="G604" s="9"/>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30962,7 +30962,7 @@
       </c>
       <c r="G605" s="9"/>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="9" t="s">
         <v>1096</v>
       </c>
@@ -30985,7 +30985,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31008,7 +31008,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31029,7 +31029,7 @@
       </c>
       <c r="G608" s="9"/>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="9" t="s">
         <v>1095</v>
       </c>
@@ -31050,7 +31050,7 @@
       </c>
       <c r="G609" s="9"/>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="9" t="s">
         <v>1095</v>
       </c>
@@ -31071,7 +31071,7 @@
       </c>
       <c r="G610" s="9"/>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31094,7 +31094,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31117,7 +31117,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31138,7 +31138,7 @@
       </c>
       <c r="G613" s="9"/>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31161,7 +31161,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31184,7 +31184,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31205,7 +31205,7 @@
       </c>
       <c r="G616" s="9"/>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31226,7 +31226,7 @@
       </c>
       <c r="G617" s="9"/>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31247,7 +31247,7 @@
       </c>
       <c r="G618" s="9"/>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31270,7 +31270,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31293,7 +31293,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31316,7 +31316,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31339,7 +31339,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31360,7 +31360,7 @@
       </c>
       <c r="G623" s="9"/>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31381,7 +31381,7 @@
       </c>
       <c r="G624" s="9"/>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31402,7 +31402,7 @@
       </c>
       <c r="G625" s="9"/>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="9" t="s">
         <v>1096</v>
       </c>
@@ -31423,7 +31423,7 @@
       </c>
       <c r="G626" s="9"/>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="G627" s="9"/>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31467,7 +31467,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31488,7 +31488,7 @@
       </c>
       <c r="G629" s="9"/>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31509,7 +31509,7 @@
       </c>
       <c r="G630" s="9"/>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31532,7 +31532,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="G632" s="9"/>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="G633" s="9"/>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31595,7 +31595,7 @@
       </c>
       <c r="G634" s="9"/>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31618,7 +31618,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="G636" s="9"/>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31662,7 +31662,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="9" t="s">
         <v>1056</v>
       </c>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="G638" s="9"/>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="9" t="s">
         <v>1056</v>
       </c>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="G639" s="9"/>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" s="9" t="s">
         <v>1056</v>
       </c>
@@ -31725,7 +31725,7 @@
       </c>
       <c r="G640" s="9"/>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31746,7 +31746,7 @@
       </c>
       <c r="G641" s="9"/>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31767,7 +31767,7 @@
       </c>
       <c r="G642" s="9"/>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31788,7 +31788,7 @@
       </c>
       <c r="G643" s="9"/>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31809,7 +31809,7 @@
       </c>
       <c r="G644" s="9"/>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="G645" s="9"/>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="G646" s="9"/>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" s="9" t="s">
         <v>1061</v>
       </c>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="G647" s="9"/>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31893,7 +31893,7 @@
       </c>
       <c r="G648" s="9"/>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31914,7 +31914,7 @@
       </c>
       <c r="G649" s="9"/>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31935,7 +31935,7 @@
       </c>
       <c r="G650" s="9"/>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31958,7 +31958,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="9" t="s">
         <v>1066</v>
       </c>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="G652" s="9"/>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="G653" s="9"/>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="G654" s="9"/>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32044,7 +32044,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="656" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32065,7 +32065,7 @@
       </c>
       <c r="G656" s="9"/>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32109,7 +32109,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="9" t="s">
         <v>138</v>
       </c>
@@ -32130,7 +32130,7 @@
       </c>
       <c r="G659" s="9"/>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="9" t="s">
         <v>138</v>
       </c>
@@ -32151,7 +32151,7 @@
       </c>
       <c r="G660" s="9"/>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32172,7 +32172,7 @@
       </c>
       <c r="G661" s="9"/>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32195,7 +32195,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="G663" s="9"/>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32237,7 +32237,7 @@
       </c>
       <c r="G664" s="9"/>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32258,7 +32258,7 @@
       </c>
       <c r="G665" s="9"/>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32281,7 +32281,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32304,7 +32304,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32327,7 +32327,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32348,7 +32348,7 @@
       </c>
       <c r="G669" s="9"/>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32371,7 +32371,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32394,7 +32394,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32415,7 +32415,7 @@
       </c>
       <c r="G672" s="9"/>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="G673" s="9"/>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32457,7 +32457,7 @@
       </c>
       <c r="G674" s="9"/>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="G675" s="9"/>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="G676" s="9"/>
     </row>
-    <row r="677" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="G677" s="9"/>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32543,7 +32543,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32564,7 +32564,7 @@
       </c>
       <c r="G679" s="9"/>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32585,7 +32585,7 @@
       </c>
       <c r="G680" s="9"/>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32606,7 +32606,7 @@
       </c>
       <c r="G681" s="9"/>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="G682" s="9"/>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32648,7 +32648,7 @@
       </c>
       <c r="G683" s="9"/>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="9" t="s">
         <v>1061</v>
       </c>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="G684" s="9"/>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="9" t="s">
         <v>1061</v>
       </c>
@@ -32690,7 +32690,7 @@
       </c>
       <c r="G685" s="9"/>
     </row>
-    <row r="686" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32711,7 +32711,7 @@
       </c>
       <c r="G686" s="9"/>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" s="9" t="s">
         <v>1066</v>
       </c>
@@ -32734,7 +32734,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="G688" s="9"/>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32776,7 +32776,7 @@
       </c>
       <c r="G689" s="9"/>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32797,7 +32797,7 @@
       </c>
       <c r="G690" s="9"/>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32818,7 +32818,7 @@
       </c>
       <c r="G691" s="9"/>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" s="9" t="s">
         <v>1056</v>
       </c>
@@ -32839,7 +32839,7 @@
       </c>
       <c r="G692" s="9"/>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" s="9" t="s">
         <v>1096</v>
       </c>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="G693" s="9"/>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" s="9" t="s">
         <v>137</v>
       </c>
@@ -32881,7 +32881,7 @@
       </c>
       <c r="G694" s="9"/>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" s="9" t="s">
         <v>137</v>
       </c>
@@ -32902,7 +32902,7 @@
       </c>
       <c r="G695" s="9"/>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" s="9" t="s">
         <v>1046</v>
       </c>
@@ -32923,7 +32923,7 @@
       </c>
       <c r="G696" s="9"/>
     </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="9" t="s">
         <v>1046</v>
       </c>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="G697" s="9"/>
     </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="9" t="s">
         <v>138</v>
       </c>
@@ -32965,7 +32965,7 @@
       </c>
       <c r="G698" s="9"/>
     </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" s="9" t="s">
         <v>1055</v>
       </c>
@@ -32986,7 +32986,7 @@
       </c>
       <c r="G699" s="9"/>
     </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="9" t="s">
         <v>1055</v>
       </c>
@@ -33007,7 +33007,7 @@
       </c>
       <c r="G700" s="9"/>
     </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="9" t="s">
         <v>1056</v>
       </c>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="G701" s="9"/>
     </row>
-    <row r="702" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="9" t="s">
         <v>1056</v>
       </c>
@@ -33049,7 +33049,7 @@
       </c>
       <c r="G702" s="9"/>
     </row>
-    <row r="703" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" s="9" t="s">
         <v>1061</v>
       </c>
@@ -33070,7 +33070,7 @@
       </c>
       <c r="G703" s="9"/>
     </row>
-    <row r="704" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="9" t="s">
         <v>1061</v>
       </c>
@@ -33091,7 +33091,7 @@
       </c>
       <c r="G704" s="9"/>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="9" t="s">
         <v>1061</v>
       </c>
@@ -33112,7 +33112,7 @@
       </c>
       <c r="G705" s="9"/>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="9" t="s">
         <v>1066</v>
       </c>
@@ -33133,7 +33133,7 @@
       </c>
       <c r="G706" s="9"/>
     </row>
-    <row r="707" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="9" t="s">
         <v>1066</v>
       </c>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="G707" s="9"/>
     </row>
-    <row r="708" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="9" t="s">
         <v>1066</v>
       </c>
@@ -33177,7 +33177,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="709" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="9" t="s">
         <v>1066</v>
       </c>
@@ -33200,7 +33200,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="9" t="s">
         <v>1093</v>
       </c>
@@ -33221,7 +33221,7 @@
       </c>
       <c r="G710" s="9"/>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="9" t="s">
         <v>1093</v>
       </c>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="G711" s="9"/>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="9" t="s">
         <v>1093</v>
       </c>
@@ -33263,7 +33263,7 @@
       </c>
       <c r="G712" s="9"/>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33286,7 +33286,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33309,7 +33309,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="G715" s="9"/>
     </row>
-    <row r="716" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33353,7 +33353,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33376,7 +33376,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33397,7 +33397,7 @@
       </c>
       <c r="G718" s="9"/>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="G719" s="9"/>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33439,7 +33439,7 @@
       </c>
       <c r="G720" s="9"/>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" s="9" t="s">
         <v>1096</v>
       </c>
@@ -33460,7 +33460,7 @@
       </c>
       <c r="G721" s="9"/>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" s="9" t="s">
         <v>1056</v>
       </c>
@@ -33481,7 +33481,7 @@
       </c>
       <c r="G722" s="9"/>
     </row>
-    <row r="723" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" s="9" t="s">
         <v>1056</v>
       </c>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="G723" s="9"/>
     </row>
-    <row r="724" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33523,7 +33523,7 @@
       </c>
       <c r="G724" s="9"/>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33544,7 +33544,7 @@
       </c>
       <c r="G725" s="9"/>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33565,7 +33565,7 @@
       </c>
       <c r="G726" s="9"/>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="G727" s="9"/>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33607,7 +33607,7 @@
       </c>
       <c r="G728" s="9"/>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33628,7 +33628,7 @@
       </c>
       <c r="G729" s="9"/>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33649,7 +33649,7 @@
       </c>
       <c r="G730" s="9"/>
     </row>
-    <row r="731" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" s="9" t="s">
         <v>1196</v>
       </c>
@@ -33670,7 +33670,7 @@
       </c>
       <c r="G731" s="9"/>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33691,7 +33691,7 @@
       </c>
       <c r="G732" s="9"/>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33712,7 +33712,7 @@
       </c>
       <c r="G733" s="9"/>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33733,7 +33733,7 @@
       </c>
       <c r="G734" s="9"/>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33754,7 +33754,7 @@
       </c>
       <c r="G735" s="9"/>
     </row>
-    <row r="736" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="G736" s="9"/>
     </row>
-    <row r="737" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33796,7 +33796,7 @@
       </c>
       <c r="G737" s="9"/>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33817,7 +33817,7 @@
       </c>
       <c r="G738" s="9"/>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33838,7 +33838,7 @@
       </c>
       <c r="G739" s="9"/>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33859,7 +33859,7 @@
       </c>
       <c r="G740" s="9"/>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33880,7 +33880,7 @@
       </c>
       <c r="G741" s="9"/>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33901,7 +33901,7 @@
       </c>
       <c r="G742" s="9"/>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33922,7 +33922,7 @@
       </c>
       <c r="G743" s="9"/>
     </row>
-    <row r="744" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="G744" s="9"/>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="G745" s="9"/>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" s="9" t="s">
         <v>1197</v>
       </c>
@@ -33985,7 +33985,7 @@
       </c>
       <c r="G746" s="9"/>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34006,7 +34006,7 @@
       </c>
       <c r="G747" s="9"/>
     </row>
-    <row r="748" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34027,7 +34027,7 @@
       </c>
       <c r="G748" s="9"/>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="G749" s="9"/>
     </row>
-    <row r="750" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34069,7 +34069,7 @@
       </c>
       <c r="G750" s="9"/>
     </row>
-    <row r="751" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34090,7 +34090,7 @@
       </c>
       <c r="G751" s="9"/>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="G752" s="9"/>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34132,7 +34132,7 @@
       </c>
       <c r="G753" s="9"/>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34153,7 +34153,7 @@
       </c>
       <c r="G754" s="9"/>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34174,7 +34174,7 @@
       </c>
       <c r="G755" s="9"/>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34195,7 +34195,7 @@
       </c>
       <c r="G756" s="9"/>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34216,7 +34216,7 @@
       </c>
       <c r="G757" s="9"/>
     </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="G758" s="9"/>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34258,7 +34258,7 @@
       </c>
       <c r="G759" s="9"/>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="G760" s="9"/>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="G761" s="9"/>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="G762" s="9"/>
     </row>
-    <row r="763" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G763" s="9"/>
     </row>
-    <row r="764" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34363,7 +34363,7 @@
       </c>
       <c r="G764" s="9"/>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34384,7 +34384,7 @@
       </c>
       <c r="G765" s="9"/>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34405,7 +34405,7 @@
       </c>
       <c r="G766" s="9"/>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34426,7 +34426,7 @@
       </c>
       <c r="G767" s="9"/>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34447,7 +34447,7 @@
       </c>
       <c r="G768" s="9"/>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34468,7 +34468,7 @@
       </c>
       <c r="G769" s="9"/>
     </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34489,7 +34489,7 @@
       </c>
       <c r="G770" s="9"/>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34510,7 +34510,7 @@
       </c>
       <c r="G771" s="9"/>
     </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34531,7 +34531,7 @@
       </c>
       <c r="G772" s="9"/>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34552,7 +34552,7 @@
       </c>
       <c r="G773" s="9"/>
     </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34573,7 +34573,7 @@
       </c>
       <c r="G774" s="9"/>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="G775" s="9"/>
     </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34615,7 +34615,7 @@
       </c>
       <c r="G776" s="9"/>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34636,7 +34636,7 @@
       </c>
       <c r="G777" s="9"/>
     </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="G778" s="9"/>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34678,7 +34678,7 @@
       </c>
       <c r="G779" s="9"/>
     </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34699,7 +34699,7 @@
       </c>
       <c r="G780" s="9"/>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34720,7 +34720,7 @@
       </c>
       <c r="G781" s="9"/>
     </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34741,7 +34741,7 @@
       </c>
       <c r="G782" s="9"/>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34762,7 +34762,7 @@
       </c>
       <c r="G783" s="9"/>
     </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34783,7 +34783,7 @@
       </c>
       <c r="G784" s="9"/>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34804,7 +34804,7 @@
       </c>
       <c r="G785" s="9"/>
     </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34825,7 +34825,7 @@
       </c>
       <c r="G786" s="9"/>
     </row>
-    <row r="787" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:7" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34846,7 +34846,7 @@
       </c>
       <c r="G787" s="9"/>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="G788" s="9"/>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34888,7 +34888,7 @@
       </c>
       <c r="G789" s="9"/>
     </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34909,7 +34909,7 @@
       </c>
       <c r="G790" s="9"/>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="G791" s="9"/>
     </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34951,7 +34951,7 @@
       </c>
       <c r="G792" s="9"/>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34972,7 +34972,7 @@
       </c>
       <c r="G793" s="9"/>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="9" t="s">
         <v>1197</v>
       </c>
@@ -34993,7 +34993,7 @@
       </c>
       <c r="G794" s="9"/>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" s="9" t="s">
         <v>1197</v>
       </c>
@@ -35014,7 +35014,7 @@
       </c>
       <c r="G795" s="9"/>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="9" t="s">
         <v>1197</v>
       </c>
@@ -35035,7 +35035,7 @@
       </c>
       <c r="G796" s="9"/>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="9" t="s">
         <v>1197</v>
       </c>
@@ -35056,7 +35056,7 @@
       </c>
       <c r="G797" s="9"/>
     </row>
-    <row r="798" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35077,7 +35077,7 @@
       </c>
       <c r="G798" s="9"/>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35100,7 +35100,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="800" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35121,7 +35121,7 @@
       </c>
       <c r="G800" s="9"/>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35142,7 +35142,7 @@
       </c>
       <c r="G801" s="9"/>
     </row>
-    <row r="802" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35163,7 +35163,7 @@
       </c>
       <c r="G802" s="9"/>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35184,7 +35184,7 @@
       </c>
       <c r="G803" s="9"/>
     </row>
-    <row r="804" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="G804" s="9"/>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35226,7 +35226,7 @@
       </c>
       <c r="G805" s="9"/>
     </row>
-    <row r="806" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35249,7 +35249,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35272,7 +35272,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="808" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35293,7 +35293,7 @@
       </c>
       <c r="G808" s="9"/>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35314,7 +35314,7 @@
       </c>
       <c r="G809" s="9"/>
     </row>
-    <row r="810" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35335,7 +35335,7 @@
       </c>
       <c r="G810" s="9"/>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35356,7 +35356,7 @@
       </c>
       <c r="G811" s="9"/>
     </row>
-    <row r="812" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35377,7 +35377,7 @@
       </c>
       <c r="G812" s="9"/>
     </row>
-    <row r="813" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:7" ht="49" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35400,7 +35400,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="814" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:7" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35423,7 +35423,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="815" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:7" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="9" t="s">
         <v>1198</v>
       </c>
@@ -35446,7 +35446,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="816" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:7" ht="46" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35469,7 +35469,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="817" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:7" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35492,7 +35492,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="818" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:7" ht="49" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35515,7 +35515,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="819" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:7" ht="22" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35538,7 +35538,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="820" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35561,7 +35561,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="821" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35584,7 +35584,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="822" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35607,7 +35607,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="823" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35630,7 +35630,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="824" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35653,7 +35653,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="825" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="233" t="s">
         <v>1198</v>
       </c>
@@ -35941,7 +35941,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G829" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
+  <autoFilter ref="A1:G837" xr:uid="{00000000-0009-0000-0000-00000D000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Fuel Cell"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C150">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
@@ -36401,19 +36407,19 @@
       <c r="B1" s="42" t="s">
         <v>1228</v>
       </c>
-      <c r="C1" s="265" t="s">
+      <c r="C1" s="268" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="250"/>
+      <c r="D1" s="248"/>
       <c r="E1" s="77" t="s">
         <v>1229</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="249" t="s">
+      <c r="A2" s="260" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="250"/>
+      <c r="B2" s="248"/>
       <c r="C2" s="117" t="s">
         <v>1230</v>
       </c>
@@ -36425,10 +36431,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="268" t="s">
+      <c r="A3" s="271" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="257"/>
+      <c r="B3" s="253"/>
       <c r="C3" s="117" t="s">
         <v>1233</v>
       </c>
@@ -36440,8 +36446,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="258"/>
-      <c r="B4" s="259"/>
+      <c r="A4" s="254"/>
+      <c r="B4" s="255"/>
       <c r="C4" s="118" t="s">
         <v>1230</v>
       </c>
@@ -36453,8 +36459,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="258"/>
-      <c r="B5" s="259"/>
+      <c r="A5" s="254"/>
+      <c r="B5" s="255"/>
       <c r="C5" s="118" t="s">
         <v>1237</v>
       </c>
@@ -36466,8 +36472,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="258"/>
-      <c r="B6" s="259"/>
+      <c r="A6" s="254"/>
+      <c r="B6" s="255"/>
       <c r="C6" s="118" t="s">
         <v>1239</v>
       </c>
@@ -36479,8 +36485,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="260"/>
-      <c r="B7" s="261"/>
+      <c r="A7" s="256"/>
+      <c r="B7" s="257"/>
       <c r="C7" s="119" t="s">
         <v>1241</v>
       </c>
@@ -36492,10 +36498,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="249" t="s">
+      <c r="A8" s="260" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="250"/>
+      <c r="B8" s="248"/>
       <c r="C8" s="120" t="s">
         <v>1243</v>
       </c>
@@ -36507,7 +36513,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="246" t="s">
+      <c r="A9" s="259" t="s">
         <v>80</v>
       </c>
       <c r="B9" s="121" t="s">
@@ -36524,7 +36530,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="247"/>
+      <c r="A10" s="250"/>
       <c r="B10" s="121" t="s">
         <v>1248</v>
       </c>
@@ -36539,8 +36545,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="247"/>
-      <c r="B11" s="264" t="s">
+      <c r="A11" s="250"/>
+      <c r="B11" s="267" t="s">
         <v>1251</v>
       </c>
       <c r="C11" s="36" t="s">
@@ -36549,26 +36555,26 @@
       <c r="D11" s="162" t="s">
         <v>1253</v>
       </c>
-      <c r="E11" s="266" t="s">
+      <c r="E11" s="269" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="248"/>
-      <c r="B12" s="248"/>
+      <c r="A12" s="251"/>
+      <c r="B12" s="251"/>
       <c r="C12" s="36" t="s">
         <v>1255</v>
       </c>
       <c r="D12" s="162" t="s">
         <v>1256</v>
       </c>
-      <c r="E12" s="248"/>
+      <c r="E12" s="251"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="246" t="s">
+      <c r="A13" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="250"/>
+      <c r="B13" s="248"/>
       <c r="C13" s="36" t="s">
         <v>1257</v>
       </c>
@@ -36580,10 +36586,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="246" t="s">
+      <c r="A14" s="259" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="250"/>
+      <c r="B14" s="248"/>
       <c r="C14" s="36" t="s">
         <v>1257</v>
       </c>
@@ -36595,10 +36601,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="246" t="s">
+      <c r="A15" s="259" t="s">
         <v>1261</v>
       </c>
-      <c r="B15" s="257"/>
+      <c r="B15" s="253"/>
       <c r="C15" s="118" t="s">
         <v>1262</v>
       </c>
@@ -36610,8 +36616,8 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="260"/>
-      <c r="B16" s="261"/>
+      <c r="A16" s="256"/>
+      <c r="B16" s="257"/>
       <c r="C16" s="118" t="s">
         <v>1264</v>
       </c>
@@ -36623,10 +36629,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="262" t="s">
+      <c r="A17" s="258" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="257"/>
+      <c r="B17" s="253"/>
       <c r="C17" s="39" t="s">
         <v>1266</v>
       </c>
@@ -36638,8 +36644,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="258"/>
-      <c r="B18" s="259"/>
+      <c r="A18" s="254"/>
+      <c r="B18" s="255"/>
       <c r="C18" s="40" t="s">
         <v>1041</v>
       </c>
@@ -36651,8 +36657,8 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="258"/>
-      <c r="B19" s="259"/>
+      <c r="A19" s="254"/>
+      <c r="B19" s="255"/>
       <c r="C19" s="40" t="s">
         <v>1269</v>
       </c>
@@ -36664,8 +36670,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="258"/>
-      <c r="B20" s="259"/>
+      <c r="A20" s="254"/>
+      <c r="B20" s="255"/>
       <c r="C20" s="39" t="s">
         <v>1271</v>
       </c>
@@ -36677,8 +36683,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="260"/>
-      <c r="B21" s="261"/>
+      <c r="A21" s="256"/>
+      <c r="B21" s="257"/>
       <c r="C21" s="40" t="s">
         <v>1273</v>
       </c>
@@ -36690,10 +36696,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="251" t="s">
+      <c r="A22" s="261" t="s">
         <v>1275</v>
       </c>
-      <c r="B22" s="250"/>
+      <c r="B22" s="248"/>
       <c r="C22" s="36" t="s">
         <v>1276</v>
       </c>
@@ -36705,10 +36711,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="251" t="s">
+      <c r="A23" s="261" t="s">
         <v>1278</v>
       </c>
-      <c r="B23" s="250"/>
+      <c r="B23" s="248"/>
       <c r="C23" s="9" t="s">
         <v>1279</v>
       </c>
@@ -36720,10 +36726,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="270" t="s">
+      <c r="A24" s="265" t="s">
         <v>99</v>
       </c>
-      <c r="B24" s="267" t="s">
+      <c r="B24" s="270" t="s">
         <v>1281</v>
       </c>
       <c r="C24" s="36" t="s">
@@ -36737,8 +36743,8 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="259"/>
-      <c r="B25" s="248"/>
+      <c r="A25" s="255"/>
+      <c r="B25" s="251"/>
       <c r="C25" s="36" t="s">
         <v>169</v>
       </c>
@@ -36750,8 +36756,8 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="259"/>
-      <c r="B26" s="263" t="s">
+      <c r="A26" s="255"/>
+      <c r="B26" s="266" t="s">
         <v>1287</v>
       </c>
       <c r="C26" s="138" t="s">
@@ -36765,8 +36771,8 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="259"/>
-      <c r="B27" s="247"/>
+      <c r="A27" s="255"/>
+      <c r="B27" s="250"/>
       <c r="C27" s="9" t="s">
         <v>1138</v>
       </c>
@@ -36776,8 +36782,8 @@
       <c r="E27" s="115"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="259"/>
-      <c r="B28" s="247"/>
+      <c r="A28" s="255"/>
+      <c r="B28" s="250"/>
       <c r="C28" s="138" t="s">
         <v>1080</v>
       </c>
@@ -36787,8 +36793,8 @@
       <c r="E28" s="115"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="259"/>
-      <c r="B29" s="248"/>
+      <c r="A29" s="255"/>
+      <c r="B29" s="251"/>
       <c r="C29" s="9" t="s">
         <v>1132</v>
       </c>
@@ -36800,8 +36806,8 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="259"/>
-      <c r="B30" s="263" t="s">
+      <c r="A30" s="255"/>
+      <c r="B30" s="266" t="s">
         <v>1293</v>
       </c>
       <c r="C30" s="36" t="s">
@@ -36815,8 +36821,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="259"/>
-      <c r="B31" s="247"/>
+      <c r="A31" s="255"/>
+      <c r="B31" s="250"/>
       <c r="C31" s="36" t="s">
         <v>206</v>
       </c>
@@ -36828,8 +36834,8 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="259"/>
-      <c r="B32" s="247"/>
+      <c r="A32" s="255"/>
+      <c r="B32" s="250"/>
       <c r="C32" s="36" t="s">
         <v>209</v>
       </c>
@@ -36841,8 +36847,8 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="259"/>
-      <c r="B33" s="248"/>
+      <c r="A33" s="255"/>
+      <c r="B33" s="251"/>
       <c r="C33" s="9" t="s">
         <v>1132</v>
       </c>
@@ -36852,8 +36858,8 @@
       <c r="E33" s="115"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="259"/>
-      <c r="B34" s="263" t="s">
+      <c r="A34" s="255"/>
+      <c r="B34" s="266" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="36" t="s">
@@ -36868,7 +36874,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="137"/>
-      <c r="B35" s="247"/>
+      <c r="B35" s="250"/>
       <c r="C35" s="36" t="s">
         <v>1221</v>
       </c>
@@ -36881,7 +36887,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="137"/>
-      <c r="B36" s="247"/>
+      <c r="B36" s="250"/>
       <c r="C36" s="36" t="s">
         <v>1302</v>
       </c>
@@ -36894,7 +36900,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="137"/>
-      <c r="B37" s="247"/>
+      <c r="B37" s="250"/>
       <c r="C37" s="36" t="s">
         <v>66</v>
       </c>
@@ -36907,7 +36913,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="137"/>
-      <c r="B38" s="248"/>
+      <c r="B38" s="251"/>
       <c r="C38" s="160" t="s">
         <v>1225</v>
       </c>
@@ -36919,10 +36925,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="269" t="s">
+      <c r="A39" s="264" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="257"/>
+      <c r="B39" s="253"/>
       <c r="C39" s="222" t="s">
         <v>1103</v>
       </c>
@@ -36934,8 +36940,8 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="258"/>
-      <c r="B40" s="259"/>
+      <c r="A40" s="254"/>
+      <c r="B40" s="255"/>
       <c r="C40" s="223" t="s">
         <v>1041</v>
       </c>
@@ -36947,8 +36953,8 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="258"/>
-      <c r="B41" s="259"/>
+      <c r="A41" s="254"/>
+      <c r="B41" s="255"/>
       <c r="C41" s="222" t="s">
         <v>1308</v>
       </c>
@@ -36960,8 +36966,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="258"/>
-      <c r="B42" s="259"/>
+      <c r="A42" s="254"/>
+      <c r="B42" s="255"/>
       <c r="C42" s="222" t="s">
         <v>1310</v>
       </c>
@@ -36973,8 +36979,8 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="258"/>
-      <c r="B43" s="259"/>
+      <c r="A43" s="254"/>
+      <c r="B43" s="255"/>
       <c r="C43" s="222" t="s">
         <v>1121</v>
       </c>
@@ -36986,8 +36992,8 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="258"/>
-      <c r="B44" s="259"/>
+      <c r="A44" s="254"/>
+      <c r="B44" s="255"/>
       <c r="C44" s="222" t="s">
         <v>1098</v>
       </c>
@@ -36999,8 +37005,8 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="258"/>
-      <c r="B45" s="259"/>
+      <c r="A45" s="254"/>
+      <c r="B45" s="255"/>
       <c r="C45" s="224" t="s">
         <v>1160</v>
       </c>
@@ -37012,8 +37018,8 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="258"/>
-      <c r="B46" s="259"/>
+      <c r="A46" s="254"/>
+      <c r="B46" s="255"/>
       <c r="C46" s="118" t="s">
         <v>1114</v>
       </c>
@@ -37025,8 +37031,8 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="258"/>
-      <c r="B47" s="259"/>
+      <c r="A47" s="254"/>
+      <c r="B47" s="255"/>
       <c r="C47" s="222" t="s">
         <v>1175</v>
       </c>
@@ -37038,8 +37044,8 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="258"/>
-      <c r="B48" s="259"/>
+      <c r="A48" s="254"/>
+      <c r="B48" s="255"/>
       <c r="C48" s="222" t="s">
         <v>1127</v>
       </c>
@@ -37051,8 +37057,8 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="258"/>
-      <c r="B49" s="259"/>
+      <c r="A49" s="254"/>
+      <c r="B49" s="255"/>
       <c r="C49" s="222" t="s">
         <v>1054</v>
       </c>
@@ -37064,8 +37070,8 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="258"/>
-      <c r="B50" s="259"/>
+      <c r="A50" s="254"/>
+      <c r="B50" s="255"/>
       <c r="C50" s="222" t="s">
         <v>1124</v>
       </c>
@@ -37077,8 +37083,8 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="258"/>
-      <c r="B51" s="259"/>
+      <c r="A51" s="254"/>
+      <c r="B51" s="255"/>
       <c r="C51" s="225" t="s">
         <v>1156</v>
       </c>
@@ -37090,8 +37096,8 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="258"/>
-      <c r="B52" s="259"/>
+      <c r="A52" s="254"/>
+      <c r="B52" s="255"/>
       <c r="C52" s="222" t="s">
         <v>1069</v>
       </c>
@@ -37103,8 +37109,8 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="258"/>
-      <c r="B53" s="259"/>
+      <c r="A53" s="254"/>
+      <c r="B53" s="255"/>
       <c r="C53" s="222" t="s">
         <v>1129</v>
       </c>
@@ -37116,8 +37122,8 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="258"/>
-      <c r="B54" s="259"/>
+      <c r="A54" s="254"/>
+      <c r="B54" s="255"/>
       <c r="C54" s="222" t="s">
         <v>1195</v>
       </c>
@@ -37129,8 +37135,8 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="258"/>
-      <c r="B55" s="259"/>
+      <c r="A55" s="254"/>
+      <c r="B55" s="255"/>
       <c r="C55" s="222" t="s">
         <v>1322</v>
       </c>
@@ -37142,8 +37148,8 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="258"/>
-      <c r="B56" s="259"/>
+      <c r="A56" s="254"/>
+      <c r="B56" s="255"/>
       <c r="C56" s="222" t="s">
         <v>1324</v>
       </c>
@@ -37155,8 +37161,8 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="258"/>
-      <c r="B57" s="259"/>
+      <c r="A57" s="254"/>
+      <c r="B57" s="255"/>
       <c r="C57" s="222" t="s">
         <v>1326</v>
       </c>
@@ -37168,8 +37174,8 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="258"/>
-      <c r="B58" s="259"/>
+      <c r="A58" s="254"/>
+      <c r="B58" s="255"/>
       <c r="C58" s="222" t="s">
         <v>1126</v>
       </c>
@@ -37181,8 +37187,8 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="258"/>
-      <c r="B59" s="259"/>
+      <c r="A59" s="254"/>
+      <c r="B59" s="255"/>
       <c r="C59" s="118" t="s">
         <v>1169</v>
       </c>
@@ -37191,8 +37197,8 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="258"/>
-      <c r="B60" s="259"/>
+      <c r="A60" s="254"/>
+      <c r="B60" s="255"/>
       <c r="C60" s="224" t="s">
         <v>1048</v>
       </c>
@@ -37201,8 +37207,8 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="258"/>
-      <c r="B61" s="259"/>
+      <c r="A61" s="254"/>
+      <c r="B61" s="255"/>
       <c r="C61" s="226" t="s">
         <v>168</v>
       </c>
@@ -37211,8 +37217,8 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="258"/>
-      <c r="B62" s="259"/>
+      <c r="A62" s="254"/>
+      <c r="B62" s="255"/>
       <c r="C62" s="222" t="s">
         <v>1076</v>
       </c>
@@ -37338,6 +37344,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B7"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A39:B62"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
@@ -37348,15 +37362,7 @@
     <mergeCell ref="A17:B21"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B7"/>
-    <mergeCell ref="A15:B16"/>
     <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://www.iea.org/data-and-statistics/data-tools/critical-minerals-data-explorer" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
@@ -37394,59 +37400,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
+      <c r="A1" s="272" t="s">
         <v>1335</v>
       </c>
-      <c r="B1" s="280"/>
-      <c r="C1" s="250"/>
+      <c r="B1" s="273"/>
+      <c r="C1" s="248"/>
     </row>
     <row r="2" spans="1:41" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:41" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="287" t="s">
+      <c r="A3" s="275" t="s">
         <v>1336</v>
       </c>
-      <c r="B3" s="277"/>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="277"/>
-      <c r="I3" s="277"/>
-      <c r="J3" s="277"/>
-      <c r="K3" s="277"/>
-      <c r="L3" s="277"/>
-      <c r="M3" s="277"/>
-      <c r="N3" s="277"/>
-      <c r="O3" s="277"/>
-      <c r="P3" s="278"/>
-      <c r="R3" s="273" t="s">
+      <c r="B3" s="276"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="276"/>
+      <c r="E3" s="276"/>
+      <c r="F3" s="276"/>
+      <c r="G3" s="276"/>
+      <c r="H3" s="276"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="276"/>
+      <c r="K3" s="276"/>
+      <c r="L3" s="276"/>
+      <c r="M3" s="276"/>
+      <c r="N3" s="276"/>
+      <c r="O3" s="276"/>
+      <c r="P3" s="277"/>
+      <c r="R3" s="288" t="s">
         <v>1066</v>
       </c>
-      <c r="S3" s="274"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="274"/>
-      <c r="AA3" s="274"/>
-      <c r="AB3" s="274"/>
-      <c r="AC3" s="274"/>
-      <c r="AD3" s="274"/>
-      <c r="AE3" s="274"/>
-      <c r="AF3" s="274"/>
-      <c r="AG3" s="275"/>
-      <c r="AI3" s="276" t="s">
+      <c r="S3" s="289"/>
+      <c r="T3" s="289"/>
+      <c r="U3" s="289"/>
+      <c r="V3" s="289"/>
+      <c r="W3" s="289"/>
+      <c r="X3" s="289"/>
+      <c r="Y3" s="289"/>
+      <c r="Z3" s="289"/>
+      <c r="AA3" s="289"/>
+      <c r="AB3" s="289"/>
+      <c r="AC3" s="289"/>
+      <c r="AD3" s="289"/>
+      <c r="AE3" s="289"/>
+      <c r="AF3" s="289"/>
+      <c r="AG3" s="290"/>
+      <c r="AI3" s="280" t="s">
         <v>1061</v>
       </c>
-      <c r="AJ3" s="277"/>
-      <c r="AK3" s="277"/>
-      <c r="AL3" s="277"/>
-      <c r="AM3" s="277"/>
-      <c r="AN3" s="277"/>
-      <c r="AO3" s="278"/>
+      <c r="AJ3" s="276"/>
+      <c r="AK3" s="276"/>
+      <c r="AL3" s="276"/>
+      <c r="AM3" s="276"/>
+      <c r="AN3" s="276"/>
+      <c r="AO3" s="277"/>
     </row>
     <row r="4" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="53" t="s">
@@ -37497,12 +37503,12 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="274" t="s">
         <v>1337</v>
       </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="250"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="248"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
         <v>1338</v>
@@ -37565,12 +37571,12 @@
       <c r="O6" s="1"/>
       <c r="P6" s="56"/>
       <c r="R6" s="60"/>
-      <c r="T6" s="279" t="s">
+      <c r="T6" s="281" t="s">
         <v>1340</v>
       </c>
-      <c r="U6" s="280"/>
-      <c r="V6" s="280"/>
-      <c r="W6" s="250"/>
+      <c r="U6" s="273"/>
+      <c r="V6" s="273"/>
+      <c r="W6" s="248"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
@@ -37625,11 +37631,11 @@
       <c r="T7" s="24">
         <v>2020</v>
       </c>
-      <c r="U7" s="281">
+      <c r="U7" s="282">
         <v>2050</v>
       </c>
-      <c r="V7" s="280"/>
-      <c r="W7" s="250"/>
+      <c r="V7" s="273"/>
+      <c r="W7" s="248"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
@@ -37894,12 +37900,12 @@
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="60"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="271" t="s">
+      <c r="C12" s="274" t="s">
         <v>1349</v>
       </c>
-      <c r="D12" s="280"/>
-      <c r="E12" s="280"/>
-      <c r="F12" s="250"/>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="248"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -38078,9 +38084,9 @@
       <c r="T15" s="284" t="s">
         <v>1066</v>
       </c>
-      <c r="U15" s="280"/>
-      <c r="V15" s="280"/>
-      <c r="W15" s="250"/>
+      <c r="U15" s="273"/>
+      <c r="V15" s="273"/>
+      <c r="W15" s="248"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -38331,14 +38337,14 @@
     <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A20" s="60"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="288" t="s">
+      <c r="C20" s="278" t="s">
         <v>1351</v>
       </c>
-      <c r="D20" s="280"/>
-      <c r="E20" s="280"/>
-      <c r="F20" s="280"/>
-      <c r="G20" s="280"/>
-      <c r="H20" s="250"/>
+      <c r="D20" s="273"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="273"/>
+      <c r="G20" s="273"/>
+      <c r="H20" s="248"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -38383,18 +38389,18 @@
     <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A21" s="60"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="271" t="s">
+      <c r="C21" s="274" t="s">
         <v>1352</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="E21" s="271" t="s">
+      <c r="D21" s="248"/>
+      <c r="E21" s="274" t="s">
         <v>1353</v>
       </c>
-      <c r="F21" s="250"/>
-      <c r="G21" s="271" t="s">
+      <c r="F21" s="248"/>
+      <c r="G21" s="274" t="s">
         <v>1354</v>
       </c>
-      <c r="H21" s="250"/>
+      <c r="H21" s="248"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -39018,11 +39024,11 @@
       <c r="C47" s="31"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A48" s="282" t="s">
+      <c r="A48" s="272" t="s">
         <v>1358</v>
       </c>
-      <c r="B48" s="280"/>
-      <c r="C48" s="250"/>
+      <c r="B48" s="273"/>
+      <c r="C48" s="248"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B49" s="31"/>
@@ -39035,18 +39041,18 @@
       <c r="B50" s="283" t="s">
         <v>1360</v>
       </c>
-      <c r="C50" s="280"/>
-      <c r="D50" s="280"/>
-      <c r="E50" s="280"/>
-      <c r="F50" s="280"/>
-      <c r="G50" s="280"/>
-      <c r="H50" s="250"/>
+      <c r="C50" s="273"/>
+      <c r="D50" s="273"/>
+      <c r="E50" s="273"/>
+      <c r="F50" s="273"/>
+      <c r="G50" s="273"/>
+      <c r="H50" s="248"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="265" t="s">
+      <c r="A51" s="268" t="s">
         <v>1361</v>
       </c>
-      <c r="B51" s="250"/>
+      <c r="B51" s="248"/>
       <c r="C51" s="43" t="s">
         <v>1362</v>
       </c>
@@ -39174,11 +39180,11 @@
       <c r="C56" s="31"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="265" t="s">
+      <c r="A57" s="268" t="s">
         <v>1372</v>
       </c>
-      <c r="B57" s="280"/>
-      <c r="C57" s="250"/>
+      <c r="B57" s="273"/>
+      <c r="C57" s="248"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
@@ -39225,32 +39231,32 @@
       <c r="C62" s="31"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="265" t="s">
+      <c r="A63" s="268" t="s">
         <v>1380</v>
       </c>
-      <c r="B63" s="250"/>
+      <c r="B63" s="248"/>
       <c r="C63" s="43" t="s">
         <v>1381</v>
       </c>
       <c r="D63" s="35" t="s">
         <v>1382</v>
       </c>
-      <c r="E63" s="265" t="s">
+      <c r="E63" s="268" t="s">
         <v>1383</v>
       </c>
-      <c r="F63" s="250"/>
+      <c r="F63" s="248"/>
       <c r="G63" s="35" t="s">
         <v>1384</v>
       </c>
-      <c r="H63" s="289" t="s">
+      <c r="H63" s="279" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="265" t="s">
+      <c r="A64" s="268" t="s">
         <v>1385</v>
       </c>
-      <c r="B64" s="250"/>
+      <c r="B64" s="248"/>
       <c r="C64" s="43" t="s">
         <v>1362</v>
       </c>
@@ -39266,7 +39272,7 @@
       <c r="G64" s="35" t="s">
         <v>1365</v>
       </c>
-      <c r="H64" s="248"/>
+      <c r="H64" s="251"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="46" t="s">
@@ -39413,11 +39419,11 @@
       <c r="H70" s="1"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="282" t="s">
+      <c r="A71" s="272" t="s">
         <v>1387</v>
       </c>
-      <c r="B71" s="280"/>
-      <c r="C71" s="250"/>
+      <c r="B71" s="273"/>
+      <c r="C71" s="248"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B72" s="31"/>
@@ -39495,11 +39501,11 @@
       <c r="C78" s="31"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="265" t="s">
+      <c r="A79" s="268" t="s">
         <v>1372</v>
       </c>
-      <c r="B79" s="280"/>
-      <c r="C79" s="250"/>
+      <c r="B79" s="273"/>
+      <c r="C79" s="248"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
@@ -39540,7 +39546,7 @@
       <c r="C83" s="31"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="272" t="s">
+      <c r="A84" s="287" t="s">
         <v>1398</v>
       </c>
       <c r="B84" s="35" t="s">
@@ -39558,7 +39564,7 @@
       <c r="F84" s="34"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="261"/>
+      <c r="A85" s="257"/>
       <c r="B85" s="35">
         <v>2020</v>
       </c>
@@ -39652,14 +39658,9 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="R3:AG3"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="AI3:AO3"/>
     <mergeCell ref="T6:W6"/>
     <mergeCell ref="U7:W7"/>
@@ -39674,9 +39675,14 @@
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="R3:AG3"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -46590,10 +46596,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="246" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="290" t="s">
+      <c r="B1" s="246" t="s">
         <v>233</v>
       </c>
     </row>
@@ -51215,7 +51221,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:AF81"/>
@@ -51333,7 +51339,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>2010</v>
       </c>
@@ -51529,7 +51535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>2010</v>
       </c>
@@ -51627,7 +51633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2010</v>
       </c>
@@ -51725,7 +51731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>2010</v>
       </c>
@@ -51823,7 +51829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>2010</v>
       </c>
@@ -51921,7 +51927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>2010</v>
       </c>
@@ -52019,7 +52025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>2010</v>
       </c>
@@ -52117,7 +52123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>2010</v>
       </c>
@@ -52215,7 +52221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>2010</v>
       </c>
@@ -52313,7 +52319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>2010</v>
       </c>
@@ -52411,7 +52417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>2010</v>
       </c>
@@ -52509,7 +52515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>2010</v>
       </c>
@@ -52607,7 +52613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>2020</v>
       </c>
@@ -52803,7 +52809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>2020</v>
       </c>
@@ -52901,7 +52907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>2020</v>
       </c>
@@ -52999,7 +53005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>2020</v>
       </c>
@@ -53097,7 +53103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>2020</v>
       </c>
@@ -53195,7 +53201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>2020</v>
       </c>
@@ -53293,7 +53299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>2020</v>
       </c>
@@ -53391,7 +53397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>2020</v>
       </c>
@@ -53489,7 +53495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>2020</v>
       </c>
@@ -53587,7 +53593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>2020</v>
       </c>
@@ -53685,7 +53691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>2020</v>
       </c>
@@ -53783,7 +53789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>2020</v>
       </c>
@@ -53881,7 +53887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>2030</v>
       </c>
@@ -54077,7 +54083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>2030</v>
       </c>
@@ -54175,7 +54181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>2030</v>
       </c>
@@ -54273,7 +54279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>2030</v>
       </c>
@@ -54371,7 +54377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>2030</v>
       </c>
@@ -54469,7 +54475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>2030</v>
       </c>
@@ -54567,7 +54573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>2030</v>
       </c>
@@ -54665,7 +54671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>2030</v>
       </c>
@@ -54763,7 +54769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>2030</v>
       </c>
@@ -54861,7 +54867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>2030</v>
       </c>
@@ -54959,7 +54965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>2030</v>
       </c>
@@ -55057,7 +55063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>2030</v>
       </c>
@@ -55155,7 +55161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>2040</v>
       </c>
@@ -55351,7 +55357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>2040</v>
       </c>
@@ -55449,7 +55455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>2040</v>
       </c>
@@ -55547,7 +55553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>2040</v>
       </c>
@@ -55645,7 +55651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>2040</v>
       </c>
@@ -55743,7 +55749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>2040</v>
       </c>
@@ -55841,7 +55847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>2040</v>
       </c>
@@ -55939,7 +55945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>2040</v>
       </c>
@@ -56037,7 +56043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>2040</v>
       </c>
@@ -56135,7 +56141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>2040</v>
       </c>
@@ -56233,7 +56239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>2040</v>
       </c>
@@ -56331,7 +56337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>2040</v>
       </c>
@@ -56429,7 +56435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>2050</v>
       </c>
@@ -56625,7 +56631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>2050</v>
       </c>
@@ -56723,7 +56729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>2050</v>
       </c>
@@ -56821,7 +56827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>2050</v>
       </c>
@@ -56919,7 +56925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>2050</v>
       </c>
@@ -57017,7 +57023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>2050</v>
       </c>
@@ -57115,7 +57121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>2050</v>
       </c>
@@ -57213,7 +57219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>2050</v>
       </c>
@@ -57311,7 +57317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>2050</v>
       </c>
@@ -57409,7 +57415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>2050</v>
       </c>
@@ -57507,7 +57513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>2050</v>
       </c>
@@ -57605,7 +57611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>2050</v>
       </c>
@@ -57703,7 +57709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>2010</v>
       </c>
@@ -57801,7 +57807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>2020</v>
       </c>
@@ -57899,7 +57905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>2030</v>
       </c>
@@ -57997,7 +58003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>2040</v>
       </c>
@@ -58095,7 +58101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>2050</v>
       </c>
@@ -58193,7 +58199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>2010</v>
       </c>
@@ -58291,7 +58297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>2020</v>
       </c>
@@ -58389,7 +58395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>2030</v>
       </c>
@@ -58487,7 +58493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>2040</v>
       </c>
@@ -58585,7 +58591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>2050</v>
       </c>
@@ -58683,7 +58689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>2010</v>
       </c>
@@ -58781,7 +58787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>2020</v>
       </c>
@@ -58879,7 +58885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>2030</v>
       </c>
@@ -58977,7 +58983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>2040</v>
       </c>
@@ -59075,7 +59081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>2050</v>
       </c>
@@ -59174,7 +59180,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AF81" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Electricity_Coal"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D385D5CB-BAEC-B24F-898F-C9A781766BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83E4A86-7D63-A142-A9F4-DA02180FA6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="37800" windowHeight="19500" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19540" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -6030,11 +6030,29 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6048,50 +6066,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6104,15 +6105,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>1085</v>
       </c>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>1085</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
         <v>1085</v>
       </c>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="G147" s="9"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9" t="s">
         <v>1085</v>
       </c>
@@ -22964,7 +22964,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="9" t="s">
         <v>1085</v>
       </c>
@@ -22985,7 +22985,7 @@
       </c>
       <c r="G205" s="9"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9" t="s">
         <v>1085</v>
       </c>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="G206" s="9"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="9" t="s">
         <v>1085</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="9" t="s">
         <v>1085</v>
       </c>
@@ -24425,7 +24425,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="9" t="s">
         <v>1085</v>
       </c>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="G279" s="9"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="9" t="s">
         <v>1085</v>
       </c>
@@ -25971,7 +25971,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="9" t="s">
         <v>1085</v>
       </c>
@@ -25994,7 +25994,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G343" s="9"/>
     </row>
-    <row r="344" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26803,7 +26803,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26824,7 +26824,7 @@
       </c>
       <c r="G380" s="9"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26845,7 +26845,7 @@
       </c>
       <c r="G381" s="9"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26868,7 +26868,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="9" t="s">
         <v>1085</v>
       </c>
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G383" s="9"/>
     </row>
-    <row r="384" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="9" t="s">
         <v>1085</v>
       </c>
@@ -30384,7 +30384,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="9" t="s">
         <v>1085</v>
       </c>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="G545" s="9"/>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="9" t="s">
         <v>1085</v>
       </c>
@@ -30428,7 +30428,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="9" t="s">
         <v>1085</v>
       </c>
@@ -31612,7 +31612,7 @@
       </c>
       <c r="G600" s="9"/>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32333,7 +32333,7 @@
       </c>
       <c r="G633" s="9"/>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="G634" s="9"/>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32377,7 +32377,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32398,7 +32398,7 @@
       </c>
       <c r="G636" s="9"/>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32652,7 +32652,7 @@
       </c>
       <c r="G648" s="9"/>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32673,7 +32673,7 @@
       </c>
       <c r="G649" s="9"/>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32694,7 +32694,7 @@
       </c>
       <c r="G650" s="9"/>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32717,7 +32717,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32738,7 +32738,7 @@
       </c>
       <c r="G652" s="9"/>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32759,7 +32759,7 @@
       </c>
       <c r="G653" s="9"/>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="G654" s="9"/>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="9" t="s">
         <v>1085</v>
       </c>
@@ -32803,7 +32803,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="656" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="9" t="s">
         <v>1085</v>
       </c>
@@ -33237,7 +33237,7 @@
       </c>
       <c r="G675" s="9"/>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="9" t="s">
         <v>1085</v>
       </c>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="G676" s="9"/>
     </row>
-    <row r="677" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="9" t="s">
         <v>1085</v>
       </c>
@@ -33449,7 +33449,7 @@
       </c>
       <c r="G685" s="9"/>
     </row>
-    <row r="686" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="9" t="s">
         <v>1085</v>
       </c>
@@ -33892,7 +33892,7 @@
       </c>
       <c r="G706" s="9"/>
     </row>
-    <row r="707" spans="1:7" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:7" ht="64" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="9" t="s">
         <v>1085</v>
       </c>
@@ -35731,7 +35731,7 @@
       </c>
       <c r="G793" s="9"/>
     </row>
-    <row r="794" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A794" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35752,7 +35752,7 @@
       </c>
       <c r="G794" s="9"/>
     </row>
-    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A795" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35773,7 +35773,7 @@
       </c>
       <c r="G795" s="9"/>
     </row>
-    <row r="796" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A796" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35794,7 +35794,7 @@
       </c>
       <c r="G796" s="9"/>
     </row>
-    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A797" s="9" t="s">
         <v>1221</v>
       </c>
@@ -36031,7 +36031,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="808" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A808" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36094,7 +36094,7 @@
       </c>
       <c r="G810" s="9"/>
     </row>
-    <row r="811" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A811" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36519,7 +36519,7 @@
       </c>
       <c r="G829" s="9"/>
     </row>
-    <row r="830" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A830" s="226" t="s">
         <v>1138</v>
       </c>
@@ -36701,9 +36701,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G837" xr:uid="{00000000-0009-0000-0000-00000C000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="c-Si"/>
+        <filter val="Platinum"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -37166,7 +37166,7 @@
       <c r="B1" s="41" t="s">
         <v>1253</v>
       </c>
-      <c r="C1" s="277" t="s">
+      <c r="C1" s="283" t="s">
         <v>63</v>
       </c>
       <c r="D1" s="272"/>
@@ -37175,7 +37175,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="280" t="s">
+      <c r="A2" s="274" t="s">
         <v>1255</v>
       </c>
       <c r="B2" s="272"/>
@@ -37190,7 +37190,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="281" t="s">
+      <c r="A3" s="286" t="s">
         <v>1259</v>
       </c>
       <c r="B3" s="266"/>
@@ -37257,7 +37257,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="280" t="s">
+      <c r="A8" s="274" t="s">
         <v>1270</v>
       </c>
       <c r="B8" s="272"/>
@@ -37272,7 +37272,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="282" t="s">
+      <c r="A9" s="277" t="s">
         <v>82</v>
       </c>
       <c r="B9" s="115" t="s">
@@ -37289,7 +37289,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="274"/>
+      <c r="A10" s="278"/>
       <c r="B10" s="115" t="s">
         <v>1276</v>
       </c>
@@ -37304,8 +37304,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="274"/>
-      <c r="B11" s="276" t="s">
+      <c r="A11" s="278"/>
+      <c r="B11" s="282" t="s">
         <v>1279</v>
       </c>
       <c r="C11" s="36" t="s">
@@ -37314,23 +37314,23 @@
       <c r="D11" s="156" t="s">
         <v>1281</v>
       </c>
-      <c r="E11" s="278" t="s">
+      <c r="E11" s="284" t="s">
         <v>1282</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="275"/>
-      <c r="B12" s="275"/>
+      <c r="A12" s="279"/>
+      <c r="B12" s="279"/>
       <c r="C12" s="36" t="s">
         <v>1283</v>
       </c>
       <c r="D12" s="156" t="s">
         <v>1284</v>
       </c>
-      <c r="E12" s="275"/>
+      <c r="E12" s="279"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="282" t="s">
+      <c r="A13" s="277" t="s">
         <v>1285</v>
       </c>
       <c r="B13" s="272"/>
@@ -37345,7 +37345,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="282" t="s">
+      <c r="A14" s="277" t="s">
         <v>1289</v>
       </c>
       <c r="B14" s="272"/>
@@ -37360,7 +37360,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="282" t="s">
+      <c r="A15" s="277" t="s">
         <v>1291</v>
       </c>
       <c r="B15" s="266"/>
@@ -37388,7 +37388,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="286" t="s">
+      <c r="A17" s="281" t="s">
         <v>1296</v>
       </c>
       <c r="B17" s="266"/>
@@ -37455,7 +37455,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="283" t="s">
+      <c r="A22" s="276" t="s">
         <v>1306</v>
       </c>
       <c r="B22" s="272"/>
@@ -37470,7 +37470,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="283" t="s">
+      <c r="A23" s="276" t="s">
         <v>1309</v>
       </c>
       <c r="B23" s="272"/>
@@ -37485,10 +37485,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="285" t="s">
+      <c r="A24" s="275" t="s">
         <v>1312</v>
       </c>
-      <c r="B24" s="279" t="s">
+      <c r="B24" s="285" t="s">
         <v>1313</v>
       </c>
       <c r="C24" s="36" t="s">
@@ -37503,7 +37503,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="268"/>
-      <c r="B25" s="275"/>
+      <c r="B25" s="279"/>
       <c r="C25" s="36" t="s">
         <v>1317</v>
       </c>
@@ -37516,7 +37516,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="268"/>
-      <c r="B26" s="273" t="s">
+      <c r="B26" s="280" t="s">
         <v>1320</v>
       </c>
       <c r="C26" s="132" t="s">
@@ -37531,7 +37531,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="268"/>
-      <c r="B27" s="274"/>
+      <c r="B27" s="278"/>
       <c r="C27" s="9" t="s">
         <v>1161</v>
       </c>
@@ -37542,7 +37542,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="268"/>
-      <c r="B28" s="274"/>
+      <c r="B28" s="278"/>
       <c r="C28" s="132" t="s">
         <v>1100</v>
       </c>
@@ -37553,7 +37553,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="268"/>
-      <c r="B29" s="275"/>
+      <c r="B29" s="279"/>
       <c r="C29" s="9" t="s">
         <v>1155</v>
       </c>
@@ -37566,7 +37566,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="268"/>
-      <c r="B30" s="273" t="s">
+      <c r="B30" s="280" t="s">
         <v>1326</v>
       </c>
       <c r="C30" s="36" t="s">
@@ -37581,7 +37581,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="268"/>
-      <c r="B31" s="274"/>
+      <c r="B31" s="278"/>
       <c r="C31" s="36" t="s">
         <v>1117</v>
       </c>
@@ -37594,7 +37594,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="268"/>
-      <c r="B32" s="274"/>
+      <c r="B32" s="278"/>
       <c r="C32" s="36" t="s">
         <v>1191</v>
       </c>
@@ -37607,7 +37607,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="268"/>
-      <c r="B33" s="275"/>
+      <c r="B33" s="279"/>
       <c r="C33" s="9" t="s">
         <v>1155</v>
       </c>
@@ -37618,7 +37618,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="268"/>
-      <c r="B34" s="273" t="s">
+      <c r="B34" s="280" t="s">
         <v>99</v>
       </c>
       <c r="C34" s="36" t="s">
@@ -37633,7 +37633,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="131"/>
-      <c r="B35" s="274"/>
+      <c r="B35" s="278"/>
       <c r="C35" s="36" t="s">
         <v>1245</v>
       </c>
@@ -37646,7 +37646,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="131"/>
-      <c r="B36" s="274"/>
+      <c r="B36" s="278"/>
       <c r="C36" s="36" t="s">
         <v>1335</v>
       </c>
@@ -37659,7 +37659,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="131"/>
-      <c r="B37" s="274"/>
+      <c r="B37" s="278"/>
       <c r="C37" s="36" t="s">
         <v>217</v>
       </c>
@@ -37672,7 +37672,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="131"/>
-      <c r="B38" s="275"/>
+      <c r="B38" s="279"/>
       <c r="C38" s="154" t="s">
         <v>1249</v>
       </c>
@@ -37684,7 +37684,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="284" t="s">
+      <c r="A39" s="273" t="s">
         <v>85</v>
       </c>
       <c r="B39" s="266"/>
@@ -38103,6 +38103,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B7"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A39:B62"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A24:A34"/>
@@ -38113,15 +38121,7 @@
     <mergeCell ref="A17:B21"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B7"/>
-    <mergeCell ref="A15:B16"/>
     <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://www.iea.org/data-and-statistics/data-tools/critical-minerals-data-explorer" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
@@ -38159,59 +38159,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="298" t="s">
+      <c r="A1" s="287" t="s">
         <v>1368</v>
       </c>
-      <c r="B1" s="296"/>
+      <c r="B1" s="288"/>
       <c r="C1" s="272"/>
     </row>
     <row r="2" spans="1:41" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:41" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="303" t="s">
+      <c r="A3" s="290" t="s">
         <v>1369</v>
       </c>
-      <c r="B3" s="293"/>
-      <c r="C3" s="293"/>
-      <c r="D3" s="293"/>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="293"/>
-      <c r="H3" s="293"/>
-      <c r="I3" s="293"/>
-      <c r="J3" s="293"/>
-      <c r="K3" s="293"/>
-      <c r="L3" s="293"/>
-      <c r="M3" s="293"/>
-      <c r="N3" s="293"/>
-      <c r="O3" s="293"/>
-      <c r="P3" s="294"/>
-      <c r="R3" s="289" t="s">
+      <c r="B3" s="291"/>
+      <c r="C3" s="291"/>
+      <c r="D3" s="291"/>
+      <c r="E3" s="291"/>
+      <c r="F3" s="291"/>
+      <c r="G3" s="291"/>
+      <c r="H3" s="291"/>
+      <c r="I3" s="291"/>
+      <c r="J3" s="291"/>
+      <c r="K3" s="291"/>
+      <c r="L3" s="291"/>
+      <c r="M3" s="291"/>
+      <c r="N3" s="291"/>
+      <c r="O3" s="291"/>
+      <c r="P3" s="292"/>
+      <c r="R3" s="303" t="s">
         <v>1085</v>
       </c>
-      <c r="S3" s="290"/>
-      <c r="T3" s="290"/>
-      <c r="U3" s="290"/>
-      <c r="V3" s="290"/>
-      <c r="W3" s="290"/>
-      <c r="X3" s="290"/>
-      <c r="Y3" s="290"/>
-      <c r="Z3" s="290"/>
-      <c r="AA3" s="290"/>
-      <c r="AB3" s="290"/>
-      <c r="AC3" s="290"/>
-      <c r="AD3" s="290"/>
-      <c r="AE3" s="290"/>
-      <c r="AF3" s="290"/>
-      <c r="AG3" s="291"/>
-      <c r="AI3" s="292" t="s">
+      <c r="S3" s="304"/>
+      <c r="T3" s="304"/>
+      <c r="U3" s="304"/>
+      <c r="V3" s="304"/>
+      <c r="W3" s="304"/>
+      <c r="X3" s="304"/>
+      <c r="Y3" s="304"/>
+      <c r="Z3" s="304"/>
+      <c r="AA3" s="304"/>
+      <c r="AB3" s="304"/>
+      <c r="AC3" s="304"/>
+      <c r="AD3" s="304"/>
+      <c r="AE3" s="304"/>
+      <c r="AF3" s="304"/>
+      <c r="AG3" s="305"/>
+      <c r="AI3" s="295" t="s">
         <v>1080</v>
       </c>
-      <c r="AJ3" s="293"/>
-      <c r="AK3" s="293"/>
-      <c r="AL3" s="293"/>
-      <c r="AM3" s="293"/>
-      <c r="AN3" s="293"/>
-      <c r="AO3" s="294"/>
+      <c r="AJ3" s="291"/>
+      <c r="AK3" s="291"/>
+      <c r="AL3" s="291"/>
+      <c r="AM3" s="291"/>
+      <c r="AN3" s="291"/>
+      <c r="AO3" s="292"/>
     </row>
     <row r="4" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="52" t="s">
@@ -38262,11 +38262,11 @@
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
-      <c r="C5" s="287" t="s">
+      <c r="C5" s="289" t="s">
         <v>1370</v>
       </c>
-      <c r="D5" s="296"/>
-      <c r="E5" s="296"/>
+      <c r="D5" s="288"/>
+      <c r="E5" s="288"/>
       <c r="F5" s="272"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
@@ -38330,11 +38330,11 @@
       <c r="O6" s="1"/>
       <c r="P6" s="55"/>
       <c r="R6" s="59"/>
-      <c r="T6" s="295" t="s">
+      <c r="T6" s="296" t="s">
         <v>1373</v>
       </c>
-      <c r="U6" s="296"/>
-      <c r="V6" s="296"/>
+      <c r="U6" s="288"/>
+      <c r="V6" s="288"/>
       <c r="W6" s="272"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -38393,7 +38393,7 @@
       <c r="U7" s="297">
         <v>2050</v>
       </c>
-      <c r="V7" s="296"/>
+      <c r="V7" s="288"/>
       <c r="W7" s="272"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -38659,11 +38659,11 @@
     <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="59"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="287" t="s">
+      <c r="C12" s="289" t="s">
         <v>1382</v>
       </c>
-      <c r="D12" s="296"/>
-      <c r="E12" s="296"/>
+      <c r="D12" s="288"/>
+      <c r="E12" s="288"/>
       <c r="F12" s="272"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -38787,12 +38787,12 @@
       <c r="P14" s="55"/>
       <c r="R14" s="59"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="301" t="s">
+      <c r="T14" s="300" t="s">
         <v>1383</v>
       </c>
-      <c r="U14" s="302"/>
-      <c r="V14" s="302"/>
-      <c r="W14" s="302"/>
+      <c r="U14" s="301"/>
+      <c r="V14" s="301"/>
+      <c r="W14" s="301"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -38840,11 +38840,11 @@
       <c r="P15" s="55"/>
       <c r="R15" s="59"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="300" t="s">
+      <c r="T15" s="299" t="s">
         <v>1085</v>
       </c>
-      <c r="U15" s="296"/>
-      <c r="V15" s="296"/>
+      <c r="U15" s="288"/>
+      <c r="V15" s="288"/>
       <c r="W15" s="272"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -39096,13 +39096,13 @@
     <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A20" s="59"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="304" t="s">
+      <c r="C20" s="293" t="s">
         <v>1384</v>
       </c>
-      <c r="D20" s="296"/>
-      <c r="E20" s="296"/>
-      <c r="F20" s="296"/>
-      <c r="G20" s="296"/>
+      <c r="D20" s="288"/>
+      <c r="E20" s="288"/>
+      <c r="F20" s="288"/>
+      <c r="G20" s="288"/>
       <c r="H20" s="272"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -39148,15 +39148,15 @@
     <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A21" s="59"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="287" t="s">
+      <c r="C21" s="289" t="s">
         <v>1385</v>
       </c>
       <c r="D21" s="272"/>
-      <c r="E21" s="287" t="s">
+      <c r="E21" s="289" t="s">
         <v>1386</v>
       </c>
       <c r="F21" s="272"/>
-      <c r="G21" s="287" t="s">
+      <c r="G21" s="289" t="s">
         <v>1387</v>
       </c>
       <c r="H21" s="272"/>
@@ -39783,10 +39783,10 @@
       <c r="C47" s="31"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A48" s="298" t="s">
+      <c r="A48" s="287" t="s">
         <v>1391</v>
       </c>
-      <c r="B48" s="296"/>
+      <c r="B48" s="288"/>
       <c r="C48" s="272"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -39797,18 +39797,18 @@
       <c r="A50" s="21" t="s">
         <v>1392</v>
       </c>
-      <c r="B50" s="299" t="s">
+      <c r="B50" s="298" t="s">
         <v>1393</v>
       </c>
-      <c r="C50" s="296"/>
-      <c r="D50" s="296"/>
-      <c r="E50" s="296"/>
-      <c r="F50" s="296"/>
-      <c r="G50" s="296"/>
+      <c r="C50" s="288"/>
+      <c r="D50" s="288"/>
+      <c r="E50" s="288"/>
+      <c r="F50" s="288"/>
+      <c r="G50" s="288"/>
       <c r="H50" s="272"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="277" t="s">
+      <c r="A51" s="283" t="s">
         <v>1394</v>
       </c>
       <c r="B51" s="272"/>
@@ -39939,10 +39939,10 @@
       <c r="C56" s="31"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="277" t="s">
+      <c r="A57" s="283" t="s">
         <v>1405</v>
       </c>
-      <c r="B57" s="296"/>
+      <c r="B57" s="288"/>
       <c r="C57" s="272"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -39990,7 +39990,7 @@
       <c r="C62" s="31"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="277" t="s">
+      <c r="A63" s="283" t="s">
         <v>1413</v>
       </c>
       <c r="B63" s="272"/>
@@ -40000,19 +40000,19 @@
       <c r="D63" s="35" t="s">
         <v>1415</v>
       </c>
-      <c r="E63" s="277" t="s">
+      <c r="E63" s="283" t="s">
         <v>1416</v>
       </c>
       <c r="F63" s="272"/>
       <c r="G63" s="35" t="s">
         <v>1417</v>
       </c>
-      <c r="H63" s="305" t="s">
+      <c r="H63" s="294" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="277" t="s">
+      <c r="A64" s="283" t="s">
         <v>1418</v>
       </c>
       <c r="B64" s="272"/>
@@ -40031,7 +40031,7 @@
       <c r="G64" s="35" t="s">
         <v>1398</v>
       </c>
-      <c r="H64" s="275"/>
+      <c r="H64" s="279"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
@@ -40178,10 +40178,10 @@
       <c r="H70" s="1"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="298" t="s">
+      <c r="A71" s="287" t="s">
         <v>1420</v>
       </c>
-      <c r="B71" s="296"/>
+      <c r="B71" s="288"/>
       <c r="C71" s="272"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -40260,10 +40260,10 @@
       <c r="C78" s="31"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="277" t="s">
+      <c r="A79" s="283" t="s">
         <v>1405</v>
       </c>
-      <c r="B79" s="296"/>
+      <c r="B79" s="288"/>
       <c r="C79" s="272"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -40305,7 +40305,7 @@
       <c r="C83" s="31"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="288" t="s">
+      <c r="A84" s="302" t="s">
         <v>1431</v>
       </c>
       <c r="B84" s="35" t="s">
@@ -40417,14 +40417,9 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="R3:AG3"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="AI3:AO3"/>
     <mergeCell ref="T6:W6"/>
     <mergeCell ref="U7:W7"/>
@@ -40439,9 +40434,14 @@
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="R3:AG3"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
+++ b/projects/critical_materials/excel_files/Material_intensities_energyscope.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83E4A86-7D63-A142-A9F4-DA02180FA6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5430705A-F0CF-BD48-B7B6-99EFA57CF7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19540" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="36020" windowHeight="19220" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8368" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8370" uniqueCount="1483">
   <si>
     <t>Metal_Intensity [g/vehicle]</t>
   </si>
@@ -4514,6 +4514,9 @@
   </si>
   <si>
     <t>Wind_Onshore</t>
+  </si>
+  <si>
+    <t>Hydrogen production via solid oxide electrolysis: Balancing environmental issues and material criticality, available at : https://www.sciencedirect.com/science/article/pii/S2666792424000325#tbl0004</t>
   </si>
 </sst>
 </file>
@@ -6086,6 +6089,14 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6105,14 +6116,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -35731,7 +35734,7 @@
       </c>
       <c r="G793" s="9"/>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35752,7 +35755,7 @@
       </c>
       <c r="G794" s="9"/>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35773,7 +35776,7 @@
       </c>
       <c r="G795" s="9"/>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35794,7 +35797,7 @@
       </c>
       <c r="G796" s="9"/>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="9" t="s">
         <v>1221</v>
       </c>
@@ -35985,7 +35988,7 @@
       </c>
       <c r="G805" s="9"/>
     </row>
-    <row r="806" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A806" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36008,7 +36011,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="807" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A807" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36052,7 +36055,7 @@
       </c>
       <c r="G808" s="9"/>
     </row>
-    <row r="809" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A809" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36073,7 +36076,7 @@
       </c>
       <c r="G809" s="9"/>
     </row>
-    <row r="810" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A810" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36115,7 +36118,7 @@
       </c>
       <c r="G811" s="9"/>
     </row>
-    <row r="812" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A812" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36136,7 +36139,7 @@
       </c>
       <c r="G812" s="9"/>
     </row>
-    <row r="813" spans="1:7" ht="49" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36159,7 +36162,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="814" spans="1:7" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36182,7 +36185,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="815" spans="1:7" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="9" t="s">
         <v>1222</v>
       </c>
@@ -36205,7 +36208,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="816" spans="1:7" ht="46" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="226" t="s">
         <v>1222</v>
       </c>
@@ -36228,7 +36231,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="817" spans="1:7" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="226" t="s">
         <v>1222</v>
       </c>
@@ -36251,7 +36254,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="818" spans="1:7" ht="49" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="226" t="s">
         <v>1222</v>
       </c>
@@ -36259,7 +36262,7 @@
         <v>1226</v>
       </c>
       <c r="C818" s="228" t="s">
-        <v>1215</v>
+        <v>40</v>
       </c>
       <c r="D818" s="229">
         <v>12</v>
@@ -36519,7 +36522,7 @@
       </c>
       <c r="G829" s="9"/>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" s="226" t="s">
         <v>1138</v>
       </c>
@@ -36701,9 +36704,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G837" xr:uid="{00000000-0009-0000-0000-00000C000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Platinum"/>
+        <filter val="PEM electrolyzer"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -38005,7 +38008,9 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="220"/>
+      <c r="B65" s="223"/>
       <c r="C65" s="9" t="s">
         <v>1227</v>
       </c>
@@ -38013,63 +38018,69 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C66" s="2"/>
-      <c r="D66" s="163"/>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="221"/>
+      <c r="B66" s="224"/>
+      <c r="C66" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D66" s="158" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C67" s="2"/>
       <c r="D67" s="163"/>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C68" s="2"/>
       <c r="D68" s="163"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C69" s="2"/>
       <c r="D69" s="163"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C70" s="2"/>
       <c r="D70" s="163"/>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C71" s="2"/>
       <c r="D71" s="163"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C72" s="2"/>
       <c r="D72" s="163"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C73" s="2"/>
       <c r="D73" s="163"/>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C74" s="2"/>
       <c r="D74" s="163"/>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C75" s="2"/>
       <c r="D75" s="163"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C76" s="2"/>
       <c r="D76" s="163"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C77" s="2"/>
       <c r="D77" s="163"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C78" s="2"/>
       <c r="D78" s="163"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C79" s="2"/>
       <c r="D79" s="163"/>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C80" s="2"/>
       <c r="D80" s="163"/>
     </row>
@@ -38185,25 +38196,25 @@
       <c r="N3" s="291"/>
       <c r="O3" s="291"/>
       <c r="P3" s="292"/>
-      <c r="R3" s="303" t="s">
+      <c r="R3" s="296" t="s">
         <v>1085</v>
       </c>
-      <c r="S3" s="304"/>
-      <c r="T3" s="304"/>
-      <c r="U3" s="304"/>
-      <c r="V3" s="304"/>
-      <c r="W3" s="304"/>
-      <c r="X3" s="304"/>
-      <c r="Y3" s="304"/>
-      <c r="Z3" s="304"/>
-      <c r="AA3" s="304"/>
-      <c r="AB3" s="304"/>
-      <c r="AC3" s="304"/>
-      <c r="AD3" s="304"/>
-      <c r="AE3" s="304"/>
-      <c r="AF3" s="304"/>
-      <c r="AG3" s="305"/>
-      <c r="AI3" s="295" t="s">
+      <c r="S3" s="297"/>
+      <c r="T3" s="297"/>
+      <c r="U3" s="297"/>
+      <c r="V3" s="297"/>
+      <c r="W3" s="297"/>
+      <c r="X3" s="297"/>
+      <c r="Y3" s="297"/>
+      <c r="Z3" s="297"/>
+      <c r="AA3" s="297"/>
+      <c r="AB3" s="297"/>
+      <c r="AC3" s="297"/>
+      <c r="AD3" s="297"/>
+      <c r="AE3" s="297"/>
+      <c r="AF3" s="297"/>
+      <c r="AG3" s="298"/>
+      <c r="AI3" s="299" t="s">
         <v>1080</v>
       </c>
       <c r="AJ3" s="291"/>
@@ -38330,7 +38341,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="55"/>
       <c r="R6" s="59"/>
-      <c r="T6" s="296" t="s">
+      <c r="T6" s="300" t="s">
         <v>1373</v>
       </c>
       <c r="U6" s="288"/>
@@ -38390,7 +38401,7 @@
       <c r="T7" s="24">
         <v>2020</v>
       </c>
-      <c r="U7" s="297">
+      <c r="U7" s="301">
         <v>2050</v>
       </c>
       <c r="V7" s="288"/>
@@ -38787,12 +38798,12 @@
       <c r="P14" s="55"/>
       <c r="R14" s="59"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="300" t="s">
+      <c r="T14" s="304" t="s">
         <v>1383</v>
       </c>
-      <c r="U14" s="301"/>
-      <c r="V14" s="301"/>
-      <c r="W14" s="301"/>
+      <c r="U14" s="305"/>
+      <c r="V14" s="305"/>
+      <c r="W14" s="305"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -38840,7 +38851,7 @@
       <c r="P15" s="55"/>
       <c r="R15" s="59"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="299" t="s">
+      <c r="T15" s="303" t="s">
         <v>1085</v>
       </c>
       <c r="U15" s="288"/>
@@ -39797,7 +39808,7 @@
       <c r="A50" s="21" t="s">
         <v>1392</v>
       </c>
-      <c r="B50" s="298" t="s">
+      <c r="B50" s="302" t="s">
         <v>1393</v>
       </c>
       <c r="C50" s="288"/>
@@ -40305,7 +40316,7 @@
       <c r="C83" s="31"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="302" t="s">
+      <c r="A84" s="295" t="s">
         <v>1431</v>
       </c>
       <c r="B84" s="35" t="s">
@@ -47727,6 +47738,7 @@
     <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
@@ -49169,9 +49181,7 @@
       <c r="H15" s="9">
         <v>393000</v>
       </c>
-      <c r="I15" s="9">
-        <v>650000</v>
-      </c>
+      <c r="I15" s="9"/>
       <c r="J15" s="9">
         <v>393000</v>
       </c>
@@ -60830,26 +60840,11 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B42" s="54">
-        <f>SUM(B2:B39)</f>
-        <v>1027297</v>
-      </c>
-      <c r="C42" s="54">
-        <f>SUM(C2:C39)</f>
-        <v>1200583</v>
-      </c>
-      <c r="D42" s="54">
-        <f>SUM(D2:D39)</f>
-        <v>1414428</v>
-      </c>
-      <c r="E42" s="54">
-        <f>SUM(E2:E39)</f>
-        <v>1233878</v>
-      </c>
-      <c r="F42" s="54">
-        <f>SUM(F2:F39)</f>
-        <v>980274</v>
-      </c>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -65790,7 +65785,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="9">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
